--- a/research/traditional_assets/database/data/morocco/morocco_power.xlsx
+++ b/research/traditional_assets/database/data/morocco/morocco_power.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.07998148757768682</v>
+        <v>0.07975614681743823</v>
       </c>
       <c r="C2">
-        <v>4181.40727821227</v>
+        <v>4155.603194493498</v>
       </c>
       <c r="D2">
-        <v>4167.90727821227</v>
+        <v>4184.022194493498</v>
       </c>
       <c r="E2">
-        <v>-1072.8</v>
+        <v>-1030.881</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>41.919</v>
       </c>
       <c r="G2">
         <v>13.5</v>
@@ -1451,28 +1451,28 @@
         <v>274.3</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>2.1085257</v>
       </c>
       <c r="N2">
-        <v>274.3</v>
+        <v>272.1914743</v>
       </c>
       <c r="O2">
-        <v>87.77600000000001</v>
+        <v>87.10127177600002</v>
       </c>
       <c r="P2">
-        <v>186.524</v>
+        <v>185.090202524</v>
       </c>
       <c r="Q2">
-        <v>272.824</v>
+        <v>271.390202524</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.07998148757768682</v>
+        <v>0.08021626951256386</v>
       </c>
       <c r="T2">
-        <v>0.4454993697880388</v>
+        <v>0.4485593654593102</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>130.0908971609879</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.07975614681743823</v>
+        <v>0.07953080605718962</v>
       </c>
       <c r="C3">
-        <v>4155.603194493498</v>
+        <v>4129.924208806667</v>
       </c>
       <c r="D3">
-        <v>4184.022194493498</v>
+        <v>4200.262208806666</v>
       </c>
       <c r="E3">
-        <v>-1030.881</v>
+        <v>-988.962</v>
       </c>
       <c r="F3">
-        <v>41.919</v>
+        <v>83.83799999999999</v>
       </c>
       <c r="G3">
         <v>13.5</v>
@@ -1533,28 +1533,28 @@
         <v>274.3</v>
       </c>
       <c r="M3">
-        <v>2.1085257</v>
+        <v>4.2170514</v>
       </c>
       <c r="N3">
-        <v>272.1914743</v>
+        <v>270.0829486</v>
       </c>
       <c r="O3">
-        <v>87.10127177600002</v>
+        <v>86.426543552</v>
       </c>
       <c r="P3">
-        <v>185.090202524</v>
+        <v>183.656405048</v>
       </c>
       <c r="Q3">
-        <v>271.390202524</v>
+        <v>269.956405048</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.08021626951256386</v>
+        <v>0.08045584291549962</v>
       </c>
       <c r="T3">
-        <v>0.4485593654593102</v>
+        <v>0.451681810021832</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>130.0908971609879</v>
+        <v>65.04544858049395</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.07953080605718962</v>
+        <v>0.07930546529694103</v>
       </c>
       <c r="C4">
-        <v>4129.924208806667</v>
+        <v>4104.371783507825</v>
       </c>
       <c r="D4">
-        <v>4200.262208806666</v>
+        <v>4216.628783507825</v>
       </c>
       <c r="E4">
-        <v>-988.962</v>
+        <v>-947.043</v>
       </c>
       <c r="F4">
-        <v>83.83799999999999</v>
+        <v>125.757</v>
       </c>
       <c r="G4">
         <v>13.5</v>
@@ -1615,28 +1615,28 @@
         <v>274.3</v>
       </c>
       <c r="M4">
-        <v>4.2170514</v>
+        <v>6.325577099999999</v>
       </c>
       <c r="N4">
-        <v>270.0829486</v>
+        <v>267.9744229</v>
       </c>
       <c r="O4">
-        <v>86.426543552</v>
+        <v>85.75181532800001</v>
       </c>
       <c r="P4">
-        <v>183.656405048</v>
+        <v>182.222607572</v>
       </c>
       <c r="Q4">
-        <v>269.956405048</v>
+        <v>268.522607572</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.08045584291549962</v>
+        <v>0.08070035597622786</v>
       </c>
       <c r="T4">
-        <v>0.451681810021832</v>
+        <v>0.454868634884612</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>65.04544858049395</v>
+        <v>43.36363238699597</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.07930546529694103</v>
+        <v>0.07908012453669241</v>
       </c>
       <c r="C5">
-        <v>4104.371783507825</v>
+        <v>4078.947403834819</v>
       </c>
       <c r="D5">
-        <v>4216.628783507825</v>
+        <v>4233.123403834819</v>
       </c>
       <c r="E5">
-        <v>-947.043</v>
+        <v>-905.124</v>
       </c>
       <c r="F5">
-        <v>125.757</v>
+        <v>167.676</v>
       </c>
       <c r="G5">
         <v>13.5</v>
@@ -1697,28 +1697,28 @@
         <v>274.3</v>
       </c>
       <c r="M5">
-        <v>6.325577099999999</v>
+        <v>8.4341028</v>
       </c>
       <c r="N5">
-        <v>267.9744229</v>
+        <v>265.8658972</v>
       </c>
       <c r="O5">
-        <v>85.75181532800001</v>
+        <v>85.077087104</v>
       </c>
       <c r="P5">
-        <v>182.222607572</v>
+        <v>180.788810096</v>
       </c>
       <c r="Q5">
-        <v>268.522607572</v>
+        <v>267.088810096</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.08070035597622786</v>
+        <v>0.08094996305905461</v>
       </c>
       <c r="T5">
-        <v>0.454868634884612</v>
+        <v>0.4581218519320333</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>43.36363238699597</v>
+        <v>32.52272429024697</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.07908012453669241</v>
+        <v>0.07885478377644381</v>
       </c>
       <c r="C6">
-        <v>4078.947403834819</v>
+        <v>4053.652578356591</v>
       </c>
       <c r="D6">
-        <v>4233.123403834819</v>
+        <v>4249.747578356591</v>
       </c>
       <c r="E6">
-        <v>-905.124</v>
+        <v>-863.2049999999999</v>
       </c>
       <c r="F6">
-        <v>167.676</v>
+        <v>209.595</v>
       </c>
       <c r="G6">
         <v>13.5</v>
@@ -1779,28 +1779,28 @@
         <v>274.3</v>
       </c>
       <c r="M6">
-        <v>8.4341028</v>
+        <v>10.5426285</v>
       </c>
       <c r="N6">
-        <v>265.8658972</v>
+        <v>263.7573715</v>
       </c>
       <c r="O6">
-        <v>85.077087104</v>
+        <v>84.40235888000001</v>
       </c>
       <c r="P6">
-        <v>180.788810096</v>
+        <v>179.35501262</v>
       </c>
       <c r="Q6">
-        <v>267.088810096</v>
+        <v>265.65501262</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.08094996305905461</v>
+        <v>0.0812048250278356</v>
       </c>
       <c r="T6">
-        <v>0.4581218519320333</v>
+        <v>0.4614435577594003</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>32.52272429024697</v>
+        <v>26.01817943219758</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.07885478377644381</v>
+        <v>0.07862944301619523</v>
       </c>
       <c r="C7">
-        <v>4053.652578356591</v>
+        <v>4028.488839433104</v>
       </c>
       <c r="D7">
-        <v>4249.747578356591</v>
+        <v>4266.502839433104</v>
       </c>
       <c r="E7">
-        <v>-863.2049999999999</v>
+        <v>-821.2859999999999</v>
       </c>
       <c r="F7">
-        <v>209.595</v>
+        <v>251.514</v>
       </c>
       <c r="G7">
         <v>13.5</v>
@@ -1861,28 +1861,28 @@
         <v>274.3</v>
       </c>
       <c r="M7">
-        <v>10.5426285</v>
+        <v>12.6511542</v>
       </c>
       <c r="N7">
-        <v>263.7573715</v>
+        <v>261.6488458</v>
       </c>
       <c r="O7">
-        <v>84.40235888000001</v>
+        <v>83.727630656</v>
       </c>
       <c r="P7">
-        <v>179.35501262</v>
+        <v>177.921215144</v>
       </c>
       <c r="Q7">
-        <v>265.65501262</v>
+        <v>264.221215144</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.0812048250278356</v>
+        <v>0.08146510959169706</v>
       </c>
       <c r="T7">
-        <v>0.4614435577594003</v>
+        <v>0.4648359381788388</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>26.01817943219758</v>
+        <v>21.68181619349798</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.07862944301619523</v>
+        <v>0.07840410225594664</v>
       </c>
       <c r="C8">
-        <v>4028.488839433104</v>
+        <v>4003.457743686219</v>
       </c>
       <c r="D8">
-        <v>4266.502839433104</v>
+        <v>4283.390743686219</v>
       </c>
       <c r="E8">
-        <v>-821.2859999999999</v>
+        <v>-779.367</v>
       </c>
       <c r="F8">
-        <v>251.514</v>
+        <v>293.4329999999999</v>
       </c>
       <c r="G8">
         <v>13.5</v>
@@ -1943,28 +1943,28 @@
         <v>274.3</v>
       </c>
       <c r="M8">
-        <v>12.6511542</v>
+        <v>14.7596799</v>
       </c>
       <c r="N8">
-        <v>261.6488458</v>
+        <v>259.5403201</v>
       </c>
       <c r="O8">
-        <v>83.727630656</v>
+        <v>83.05290243200001</v>
       </c>
       <c r="P8">
-        <v>177.921215144</v>
+        <v>176.487417668</v>
       </c>
       <c r="Q8">
-        <v>264.221215144</v>
+        <v>262.787417668</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.08146510959169706</v>
+        <v>0.0817309916730609</v>
       </c>
       <c r="T8">
-        <v>0.4648359381788388</v>
+        <v>0.4683012730158998</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>21.68181619349798</v>
+        <v>18.58441388014113</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.07840410225594663</v>
+        <v>0.07817876149569804</v>
       </c>
       <c r="C9">
-        <v>4003.457743686221</v>
+        <v>3978.560872481753</v>
       </c>
       <c r="D9">
-        <v>4283.390743686221</v>
+        <v>4300.412872481753</v>
       </c>
       <c r="E9">
-        <v>-779.367</v>
+        <v>-737.448</v>
       </c>
       <c r="F9">
-        <v>293.433</v>
+        <v>335.352</v>
       </c>
       <c r="G9">
         <v>13.5</v>
@@ -2025,28 +2025,28 @@
         <v>274.3</v>
       </c>
       <c r="M9">
-        <v>14.7596799</v>
+        <v>16.8682056</v>
       </c>
       <c r="N9">
-        <v>259.5403201</v>
+        <v>257.4317944</v>
       </c>
       <c r="O9">
-        <v>83.05290243200001</v>
+        <v>82.378174208</v>
       </c>
       <c r="P9">
-        <v>176.487417668</v>
+        <v>175.053620192</v>
       </c>
       <c r="Q9">
-        <v>262.787417668</v>
+        <v>261.353620192</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.0817309916730609</v>
+        <v>0.08200265379967178</v>
       </c>
       <c r="T9">
-        <v>0.4683012730158998</v>
+        <v>0.4718419412189838</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>18.58441388014113</v>
+        <v>16.26136214512348</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.07817876149569804</v>
+        <v>0.07795342073544945</v>
       </c>
       <c r="C10">
-        <v>3978.560872481753</v>
+        <v>3953.799832423108</v>
       </c>
       <c r="D10">
-        <v>4300.412872481753</v>
+        <v>4317.570832423108</v>
       </c>
       <c r="E10">
-        <v>-737.448</v>
+        <v>-695.529</v>
       </c>
       <c r="F10">
-        <v>335.352</v>
+        <v>377.271</v>
       </c>
       <c r="G10">
         <v>13.5</v>
@@ -2107,28 +2107,28 @@
         <v>274.3</v>
       </c>
       <c r="M10">
-        <v>16.8682056</v>
+        <v>18.9767313</v>
       </c>
       <c r="N10">
-        <v>257.4317944</v>
+        <v>255.3232687</v>
       </c>
       <c r="O10">
-        <v>82.378174208</v>
+        <v>81.70344598400001</v>
       </c>
       <c r="P10">
-        <v>175.053620192</v>
+        <v>173.619822716</v>
       </c>
       <c r="Q10">
-        <v>261.353620192</v>
+        <v>259.919822716</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.08200265379967178</v>
+        <v>0.08228028652247191</v>
       </c>
       <c r="T10">
-        <v>0.4718419412189838</v>
+        <v>0.4754604263056521</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>16.26136214512348</v>
+        <v>14.45454412899866</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.07795342073544945</v>
+        <v>0.07772807997520084</v>
       </c>
       <c r="C11">
-        <v>3953.799832423108</v>
+        <v>3929.176255856766</v>
       </c>
       <c r="D11">
-        <v>4317.570832423108</v>
+        <v>4334.866255856766</v>
       </c>
       <c r="E11">
-        <v>-695.529</v>
+        <v>-653.61</v>
       </c>
       <c r="F11">
-        <v>377.271</v>
+        <v>419.1899999999999</v>
       </c>
       <c r="G11">
         <v>13.5</v>
@@ -2189,28 +2189,28 @@
         <v>274.3</v>
       </c>
       <c r="M11">
-        <v>18.9767313</v>
+        <v>21.085257</v>
       </c>
       <c r="N11">
-        <v>255.3232687</v>
+        <v>253.214743</v>
       </c>
       <c r="O11">
-        <v>81.70344598400001</v>
+        <v>81.02871776000001</v>
       </c>
       <c r="P11">
-        <v>173.619822716</v>
+        <v>172.18602524</v>
       </c>
       <c r="Q11">
-        <v>259.919822716</v>
+        <v>258.48602524</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.08228028652247191</v>
+        <v>0.08256408886133426</v>
       </c>
       <c r="T11">
-        <v>0.4754604263056521</v>
+        <v>0.479159322172024</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>14.45454412899866</v>
+        <v>13.00908971609879</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.07772807997520084</v>
+        <v>0.07761493921495223</v>
       </c>
       <c r="C12">
-        <v>3929.176255856766</v>
+        <v>3895.993426982094</v>
       </c>
       <c r="D12">
-        <v>4334.866255856766</v>
+        <v>4343.602426982094</v>
       </c>
       <c r="E12">
-        <v>-653.6099999999999</v>
+        <v>-611.691</v>
       </c>
       <c r="F12">
-        <v>419.19</v>
+        <v>461.109</v>
       </c>
       <c r="G12">
         <v>13.5</v>
@@ -2271,45 +2271,45 @@
         <v>274.3</v>
       </c>
       <c r="M12">
-        <v>21.085257</v>
+        <v>23.8854462</v>
       </c>
       <c r="N12">
-        <v>253.214743</v>
+        <v>250.4145538</v>
       </c>
       <c r="O12">
-        <v>81.02871776000001</v>
+        <v>80.13265721600001</v>
       </c>
       <c r="P12">
-        <v>172.18602524</v>
+        <v>170.281896584</v>
       </c>
       <c r="Q12">
-        <v>258.48602524</v>
+        <v>256.581896584</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.08256408886133426</v>
+        <v>0.0828542687808452</v>
       </c>
       <c r="T12">
-        <v>0.479159322172024</v>
+        <v>0.48294133929382</v>
       </c>
       <c r="U12">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V12">
         <v>0.32</v>
       </c>
       <c r="W12">
-        <v>0.034204</v>
+        <v>0.035224</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y12">
-        <v>13.00908971609879</v>
+        <v>11.48398056721252</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.07761493921495223</v>
+        <v>0.07739979845470364</v>
       </c>
       <c r="C13">
-        <v>3895.993426982094</v>
+        <v>3870.784048270027</v>
       </c>
       <c r="D13">
-        <v>4343.602426982094</v>
+        <v>4360.312048270027</v>
       </c>
       <c r="E13">
-        <v>-611.691</v>
+        <v>-569.7719999999999</v>
       </c>
       <c r="F13">
-        <v>461.109</v>
+        <v>503.028</v>
       </c>
       <c r="G13">
         <v>13.5</v>
@@ -2353,28 +2353,28 @@
         <v>274.3</v>
       </c>
       <c r="M13">
-        <v>23.8854462</v>
+        <v>26.0568504</v>
       </c>
       <c r="N13">
-        <v>250.4145538</v>
+        <v>248.2431496</v>
       </c>
       <c r="O13">
-        <v>80.13265721600001</v>
+        <v>79.43780787200001</v>
       </c>
       <c r="P13">
-        <v>170.281896584</v>
+        <v>168.805341728</v>
       </c>
       <c r="Q13">
-        <v>256.581896584</v>
+        <v>255.105341728</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.0828542687808452</v>
+        <v>0.08315104369852687</v>
       </c>
       <c r="T13">
-        <v>0.48294133929382</v>
+        <v>0.4868093113502024</v>
       </c>
       <c r="U13">
         <v>0.0518</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>11.48398056721252</v>
+        <v>10.52698218661147</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.07739979845470364</v>
+        <v>0.07733493769445504</v>
       </c>
       <c r="C14">
-        <v>3870.784048270027</v>
+        <v>3833.927925838919</v>
       </c>
       <c r="D14">
-        <v>4360.312048270027</v>
+        <v>4365.374925838919</v>
       </c>
       <c r="E14">
-        <v>-569.7719999999999</v>
+        <v>-527.853</v>
       </c>
       <c r="F14">
-        <v>503.028</v>
+        <v>544.947</v>
       </c>
       <c r="G14">
         <v>13.5</v>
@@ -2435,45 +2435,45 @@
         <v>274.3</v>
       </c>
       <c r="M14">
-        <v>26.0568504</v>
+        <v>29.1546645</v>
       </c>
       <c r="N14">
-        <v>248.2431496</v>
+        <v>245.1453355</v>
       </c>
       <c r="O14">
-        <v>79.43780787200001</v>
+        <v>78.44650736000001</v>
       </c>
       <c r="P14">
-        <v>168.805341728</v>
+        <v>166.69882814</v>
       </c>
       <c r="Q14">
-        <v>255.105341728</v>
+        <v>252.99882814</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.08315104369852687</v>
+        <v>0.08345464102810925</v>
       </c>
       <c r="T14">
-        <v>0.4868093113502024</v>
+        <v>0.4907662023044327</v>
       </c>
       <c r="U14">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V14">
         <v>0.32</v>
       </c>
       <c r="W14">
-        <v>0.035224</v>
+        <v>0.03638</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y14">
-        <v>10.52698218661147</v>
+        <v>9.408443029759441</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.07733493769445504</v>
+        <v>0.07713135693420645</v>
       </c>
       <c r="C15">
-        <v>3833.927925838919</v>
+        <v>3807.976603836065</v>
       </c>
       <c r="D15">
-        <v>4365.374925838919</v>
+        <v>4381.342603836065</v>
       </c>
       <c r="E15">
-        <v>-527.853</v>
+        <v>-485.934</v>
       </c>
       <c r="F15">
-        <v>544.947</v>
+        <v>586.866</v>
       </c>
       <c r="G15">
         <v>13.5</v>
@@ -2517,28 +2517,28 @@
         <v>274.3</v>
       </c>
       <c r="M15">
-        <v>29.1546645</v>
+        <v>31.397331</v>
       </c>
       <c r="N15">
-        <v>245.1453355</v>
+        <v>242.902669</v>
       </c>
       <c r="O15">
-        <v>78.44650736000001</v>
+        <v>77.72885408</v>
       </c>
       <c r="P15">
-        <v>166.69882814</v>
+        <v>165.17381492</v>
       </c>
       <c r="Q15">
-        <v>252.99882814</v>
+        <v>251.47381492</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.08345464102810925</v>
+        <v>0.08376529876070517</v>
       </c>
       <c r="T15">
-        <v>0.4907662023044327</v>
+        <v>0.4948151139785287</v>
       </c>
       <c r="U15">
         <v>0.0535</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>9.408443029759441</v>
+        <v>8.736411384776623</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.07713135693420645</v>
+        <v>0.07692777617395785</v>
       </c>
       <c r="C16">
-        <v>3807.976603836065</v>
+        <v>3782.142523896827</v>
       </c>
       <c r="D16">
-        <v>4381.342603836065</v>
+        <v>4397.427523896827</v>
       </c>
       <c r="E16">
-        <v>-485.934</v>
+        <v>-444.0149999999999</v>
       </c>
       <c r="F16">
-        <v>586.866</v>
+        <v>628.7850000000001</v>
       </c>
       <c r="G16">
         <v>13.5</v>
@@ -2599,28 +2599,28 @@
         <v>274.3</v>
       </c>
       <c r="M16">
-        <v>31.397331</v>
+        <v>33.63999750000001</v>
       </c>
       <c r="N16">
-        <v>242.902669</v>
+        <v>240.6600025</v>
       </c>
       <c r="O16">
-        <v>77.72885408</v>
+        <v>77.01120080000001</v>
       </c>
       <c r="P16">
-        <v>165.17381492</v>
+        <v>163.6488017</v>
       </c>
       <c r="Q16">
-        <v>251.47381492</v>
+        <v>249.9488017</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.08376529876070517</v>
+        <v>0.08408326608700924</v>
       </c>
       <c r="T16">
-        <v>0.4948151139785287</v>
+        <v>0.4989592941626035</v>
       </c>
       <c r="U16">
         <v>0.0535</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>8.736411384776623</v>
+        <v>8.153983959124847</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.07692777617395785</v>
+        <v>0.07672419541370924</v>
       </c>
       <c r="C17">
-        <v>3782.142523896827</v>
+        <v>3756.426982047253</v>
       </c>
       <c r="D17">
-        <v>4397.427523896827</v>
+        <v>4413.630982047252</v>
       </c>
       <c r="E17">
-        <v>-444.015</v>
+        <v>-402.096</v>
       </c>
       <c r="F17">
-        <v>628.785</v>
+        <v>670.704</v>
       </c>
       <c r="G17">
         <v>13.5</v>
@@ -2681,28 +2681,28 @@
         <v>274.3</v>
       </c>
       <c r="M17">
-        <v>33.6399975</v>
+        <v>35.882664</v>
       </c>
       <c r="N17">
-        <v>240.6600025</v>
+        <v>238.417336</v>
       </c>
       <c r="O17">
-        <v>77.01120080000001</v>
+        <v>76.29354752</v>
       </c>
       <c r="P17">
-        <v>163.6488017</v>
+        <v>162.12378848</v>
       </c>
       <c r="Q17">
-        <v>249.9488017</v>
+        <v>248.42378848</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.08408326608700924</v>
+        <v>0.08440880406393958</v>
       </c>
       <c r="T17">
-        <v>0.4989592941626035</v>
+        <v>0.503202145303442</v>
       </c>
       <c r="U17">
         <v>0.0535</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>8.153983959124849</v>
+        <v>7.644359961679545</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.07672419541370924</v>
+        <v>0.07661309465346065</v>
       </c>
       <c r="C18">
-        <v>3756.426982047253</v>
+        <v>3723.401212359431</v>
       </c>
       <c r="D18">
-        <v>4413.630982047252</v>
+        <v>4422.524212359431</v>
       </c>
       <c r="E18">
-        <v>-402.096</v>
+        <v>-360.177</v>
       </c>
       <c r="F18">
-        <v>670.704</v>
+        <v>712.6229999999999</v>
       </c>
       <c r="G18">
         <v>13.5</v>
@@ -2763,45 +2763,45 @@
         <v>274.3</v>
       </c>
       <c r="M18">
-        <v>35.882664</v>
+        <v>38.6954289</v>
       </c>
       <c r="N18">
-        <v>238.417336</v>
+        <v>235.6045711</v>
       </c>
       <c r="O18">
-        <v>76.29354752</v>
+        <v>75.393462752</v>
       </c>
       <c r="P18">
-        <v>162.12378848</v>
+        <v>160.211108348</v>
       </c>
       <c r="Q18">
-        <v>248.42378848</v>
+        <v>246.511108348</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.08440880406393958</v>
+        <v>0.08474218632947067</v>
       </c>
       <c r="T18">
-        <v>0.503202145303442</v>
+        <v>0.5075472338211681</v>
       </c>
       <c r="U18">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V18">
         <v>0.32</v>
       </c>
       <c r="W18">
-        <v>0.03638</v>
+        <v>0.036924</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y18">
-        <v>7.644359961679545</v>
+        <v>7.088692587149487</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.07661309465346065</v>
+        <v>0.07641495389321204</v>
       </c>
       <c r="C19">
-        <v>3723.401212359431</v>
+        <v>3697.431966434608</v>
       </c>
       <c r="D19">
-        <v>4422.524212359431</v>
+        <v>4438.473966434608</v>
       </c>
       <c r="E19">
-        <v>-360.177</v>
+        <v>-318.2579999999999</v>
       </c>
       <c r="F19">
-        <v>712.6229999999999</v>
+        <v>754.542</v>
       </c>
       <c r="G19">
         <v>13.5</v>
@@ -2845,28 +2845,28 @@
         <v>274.3</v>
       </c>
       <c r="M19">
-        <v>38.6954289</v>
+        <v>40.9716306</v>
       </c>
       <c r="N19">
-        <v>235.6045711</v>
+        <v>233.3283694</v>
       </c>
       <c r="O19">
-        <v>75.393462752</v>
+        <v>74.66507820800001</v>
       </c>
       <c r="P19">
-        <v>160.211108348</v>
+        <v>158.663291192</v>
       </c>
       <c r="Q19">
-        <v>246.511108348</v>
+        <v>244.963291192</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.08474218632947067</v>
+        <v>0.0850836998697708</v>
       </c>
       <c r="T19">
-        <v>0.5075472338211681</v>
+        <v>0.5119983001076193</v>
       </c>
       <c r="U19">
         <v>0.0543</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>7.088692587149487</v>
+        <v>6.694876332307848</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.07641495389321205</v>
+        <v>0.07621681313296347</v>
       </c>
       <c r="C20">
-        <v>3697.431966434607</v>
+        <v>3671.578181922027</v>
       </c>
       <c r="D20">
-        <v>4438.473966434607</v>
+        <v>4454.539181922027</v>
       </c>
       <c r="E20">
-        <v>-318.258</v>
+        <v>-276.3390000000001</v>
       </c>
       <c r="F20">
-        <v>754.5419999999999</v>
+        <v>796.4609999999999</v>
       </c>
       <c r="G20">
         <v>13.5</v>
@@ -2927,28 +2927,28 @@
         <v>274.3</v>
       </c>
       <c r="M20">
-        <v>40.9716306</v>
+        <v>43.2478323</v>
       </c>
       <c r="N20">
-        <v>233.3283694</v>
+        <v>231.0521677</v>
       </c>
       <c r="O20">
-        <v>74.66507820800001</v>
+        <v>73.936693664</v>
       </c>
       <c r="P20">
-        <v>158.663291192</v>
+        <v>157.115474036</v>
       </c>
       <c r="Q20">
-        <v>244.963291192</v>
+        <v>243.415474036</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.0850836998697708</v>
+        <v>0.08543364584316476</v>
       </c>
       <c r="T20">
-        <v>0.5119983001076193</v>
+        <v>0.5165592692653408</v>
       </c>
       <c r="U20">
         <v>0.0543</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>6.694876332307849</v>
+        <v>6.34251442008112</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.07621681313296347</v>
+        <v>0.07615467237271485</v>
       </c>
       <c r="C21">
-        <v>3671.578181922027</v>
+        <v>3634.721526128023</v>
       </c>
       <c r="D21">
-        <v>4454.539181922027</v>
+        <v>4459.601526128024</v>
       </c>
       <c r="E21">
-        <v>-276.3390000000001</v>
+        <v>-234.42</v>
       </c>
       <c r="F21">
-        <v>796.4609999999999</v>
+        <v>838.38</v>
       </c>
       <c r="G21">
         <v>13.5</v>
@@ -3009,45 +3009,45 @@
         <v>274.3</v>
       </c>
       <c r="M21">
-        <v>43.2478323</v>
+        <v>46.362414</v>
       </c>
       <c r="N21">
-        <v>231.0521677</v>
+        <v>227.937586</v>
       </c>
       <c r="O21">
-        <v>73.936693664</v>
+        <v>72.94002752</v>
       </c>
       <c r="P21">
-        <v>157.115474036</v>
+        <v>154.99755848</v>
       </c>
       <c r="Q21">
-        <v>243.415474036</v>
+        <v>241.29755848</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.08543364584316476</v>
+        <v>0.08579234046589357</v>
       </c>
       <c r="T21">
-        <v>0.5165592692653408</v>
+        <v>0.5212342626520055</v>
       </c>
       <c r="U21">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V21">
         <v>0.32</v>
       </c>
       <c r="W21">
-        <v>0.036924</v>
+        <v>0.037604</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y21">
-        <v>6.34251442008112</v>
+        <v>5.916430494753789</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.07615467237271485</v>
+        <v>0.07596333161246627</v>
       </c>
       <c r="C22">
-        <v>3634.721526128023</v>
+        <v>3608.462760705928</v>
       </c>
       <c r="D22">
-        <v>4459.601526128024</v>
+        <v>4475.261760705928</v>
       </c>
       <c r="E22">
-        <v>-234.42</v>
+        <v>-192.501</v>
       </c>
       <c r="F22">
-        <v>838.38</v>
+        <v>880.299</v>
       </c>
       <c r="G22">
         <v>13.5</v>
@@ -3091,28 +3091,28 @@
         <v>274.3</v>
       </c>
       <c r="M22">
-        <v>46.362414</v>
+        <v>48.6805347</v>
       </c>
       <c r="N22">
-        <v>227.937586</v>
+        <v>225.6194653</v>
       </c>
       <c r="O22">
-        <v>72.94002752</v>
+        <v>72.198228896</v>
       </c>
       <c r="P22">
-        <v>154.99755848</v>
+        <v>153.421236404</v>
       </c>
       <c r="Q22">
-        <v>241.29755848</v>
+        <v>239.721236404</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.08579234046589357</v>
+        <v>0.08616011596514717</v>
       </c>
       <c r="T22">
-        <v>0.5212342626520055</v>
+        <v>0.5260276103016236</v>
       </c>
       <c r="U22">
         <v>0.0553</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>5.916430494753789</v>
+        <v>5.634695709289323</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.07596333161246627</v>
+        <v>0.07577199085221767</v>
       </c>
       <c r="C23">
-        <v>3608.462760705928</v>
+        <v>3582.314367105128</v>
       </c>
       <c r="D23">
-        <v>4475.261760705928</v>
+        <v>4491.032367105127</v>
       </c>
       <c r="E23">
-        <v>-192.5010000000001</v>
+        <v>-150.582</v>
       </c>
       <c r="F23">
-        <v>880.2989999999999</v>
+        <v>922.218</v>
       </c>
       <c r="G23">
         <v>13.5</v>
@@ -3173,28 +3173,28 @@
         <v>274.3</v>
       </c>
       <c r="M23">
-        <v>48.6805347</v>
+        <v>50.9986554</v>
       </c>
       <c r="N23">
-        <v>225.6194653</v>
+        <v>223.3013446</v>
       </c>
       <c r="O23">
-        <v>72.198228896</v>
+        <v>71.45643027200001</v>
       </c>
       <c r="P23">
-        <v>153.421236404</v>
+        <v>151.844914328</v>
       </c>
       <c r="Q23">
-        <v>239.721236404</v>
+        <v>238.144914328</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.08616011596514717</v>
+        <v>0.08653732160540727</v>
       </c>
       <c r="T23">
-        <v>0.5260276103016236</v>
+        <v>0.530943864301232</v>
       </c>
       <c r="U23">
         <v>0.0553</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>5.634695709289323</v>
+        <v>5.3785731770489</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.07577199085221767</v>
+        <v>0.07558065009196907</v>
       </c>
       <c r="C24">
-        <v>3582.314367105128</v>
+        <v>3556.27751628694</v>
       </c>
       <c r="D24">
-        <v>4491.032367105127</v>
+        <v>4506.91451628694</v>
       </c>
       <c r="E24">
-        <v>-150.582</v>
+        <v>-108.663</v>
       </c>
       <c r="F24">
-        <v>922.218</v>
+        <v>964.1369999999999</v>
       </c>
       <c r="G24">
         <v>13.5</v>
@@ -3255,28 +3255,28 @@
         <v>274.3</v>
       </c>
       <c r="M24">
-        <v>50.9986554</v>
+        <v>53.3167761</v>
       </c>
       <c r="N24">
-        <v>223.3013446</v>
+        <v>220.9832239</v>
       </c>
       <c r="O24">
-        <v>71.45643027200001</v>
+        <v>70.71463164800001</v>
       </c>
       <c r="P24">
-        <v>151.844914328</v>
+        <v>150.268592252</v>
       </c>
       <c r="Q24">
-        <v>238.144914328</v>
+        <v>236.568592252</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.08653732160540727</v>
+        <v>0.08692432479476501</v>
       </c>
       <c r="T24">
-        <v>0.530943864301232</v>
+        <v>0.5359878132099209</v>
       </c>
       <c r="U24">
         <v>0.0553</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>5.3785731770489</v>
+        <v>5.144722169351121</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.07558065009196907</v>
+        <v>0.07538930933172047</v>
       </c>
       <c r="C25">
-        <v>3556.27751628694</v>
+        <v>3530.35339583549</v>
       </c>
       <c r="D25">
-        <v>4506.91451628694</v>
+        <v>4522.90939583549</v>
       </c>
       <c r="E25">
-        <v>-108.663</v>
+        <v>-66.74399999999991</v>
       </c>
       <c r="F25">
-        <v>964.1369999999999</v>
+        <v>1006.056</v>
       </c>
       <c r="G25">
         <v>13.5</v>
@@ -3337,28 +3337,28 @@
         <v>274.3</v>
       </c>
       <c r="M25">
-        <v>53.3167761</v>
+        <v>55.63489680000001</v>
       </c>
       <c r="N25">
-        <v>220.9832239</v>
+        <v>218.6651032</v>
       </c>
       <c r="O25">
-        <v>70.71463164800001</v>
+        <v>69.972833024</v>
       </c>
       <c r="P25">
-        <v>150.268592252</v>
+        <v>148.692270176</v>
       </c>
       <c r="Q25">
-        <v>236.568592252</v>
+        <v>234.992270176</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.08692432479476501</v>
+        <v>0.08732151227857957</v>
       </c>
       <c r="T25">
-        <v>0.5359878132099209</v>
+        <v>0.5411644976162071</v>
       </c>
       <c r="U25">
         <v>0.0553</v>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>5.144722169351121</v>
+        <v>4.930358745628157</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.07538930933172047</v>
+        <v>0.07519796857147187</v>
       </c>
       <c r="C26">
-        <v>3530.35339583549</v>
+        <v>3504.543210253717</v>
       </c>
       <c r="D26">
-        <v>4522.90939583549</v>
+        <v>4539.018210253717</v>
       </c>
       <c r="E26">
-        <v>-66.74400000000003</v>
+        <v>-24.82500000000005</v>
       </c>
       <c r="F26">
-        <v>1006.056</v>
+        <v>1047.975</v>
       </c>
       <c r="G26">
         <v>13.5</v>
@@ -3419,28 +3419,28 @@
         <v>274.3</v>
       </c>
       <c r="M26">
-        <v>55.6348968</v>
+        <v>57.95301749999999</v>
       </c>
       <c r="N26">
-        <v>218.6651032</v>
+        <v>216.3469825</v>
       </c>
       <c r="O26">
-        <v>69.972833024</v>
+        <v>69.23103440000001</v>
       </c>
       <c r="P26">
-        <v>148.692270176</v>
+        <v>147.1159481</v>
       </c>
       <c r="Q26">
-        <v>234.992270176</v>
+        <v>233.4159481</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.08732151227857957</v>
+        <v>0.08772929142862916</v>
       </c>
       <c r="T26">
-        <v>0.5411644976162071</v>
+        <v>0.5464792269399943</v>
       </c>
       <c r="U26">
         <v>0.0553</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>4.930358745628158</v>
+        <v>4.733144395803032</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.07519796857147187</v>
+        <v>0.07500662781122328</v>
       </c>
       <c r="C27">
-        <v>3504.543210253717</v>
+        <v>3478.848181265752</v>
       </c>
       <c r="D27">
-        <v>4539.018210253717</v>
+        <v>4555.242181265752</v>
       </c>
       <c r="E27">
-        <v>-24.82500000000005</v>
+        <v>17.09400000000005</v>
       </c>
       <c r="F27">
-        <v>1047.975</v>
+        <v>1089.894</v>
       </c>
       <c r="G27">
         <v>13.5</v>
@@ -3501,28 +3501,28 @@
         <v>274.3</v>
       </c>
       <c r="M27">
-        <v>57.95301749999999</v>
+        <v>60.2711382</v>
       </c>
       <c r="N27">
-        <v>216.3469825</v>
+        <v>214.0288618</v>
       </c>
       <c r="O27">
-        <v>69.23103440000001</v>
+        <v>68.489235776</v>
       </c>
       <c r="P27">
-        <v>147.1159481</v>
+        <v>145.539626024</v>
       </c>
       <c r="Q27">
-        <v>233.4159481</v>
+        <v>231.839626024</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.08772929142862916</v>
+        <v>0.08814809163678822</v>
       </c>
       <c r="T27">
-        <v>0.5464792269399943</v>
+        <v>0.5519375975968568</v>
       </c>
       <c r="U27">
         <v>0.0553</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>4.733144395803032</v>
+        <v>4.551100380579838</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.07500662781122328</v>
+        <v>0.07527428705097468</v>
       </c>
       <c r="C28">
-        <v>3478.848181265752</v>
+        <v>3414.26628602984</v>
       </c>
       <c r="D28">
-        <v>4555.242181265752</v>
+        <v>4532.57928602984</v>
       </c>
       <c r="E28">
-        <v>17.09400000000005</v>
+        <v>59.01299999999992</v>
       </c>
       <c r="F28">
-        <v>1089.894</v>
+        <v>1131.813</v>
       </c>
       <c r="G28">
         <v>13.5</v>
@@ -3583,45 +3583,45 @@
         <v>274.3</v>
       </c>
       <c r="M28">
-        <v>60.2711382</v>
+        <v>65.4187914</v>
       </c>
       <c r="N28">
-        <v>214.0288618</v>
+        <v>208.8812086</v>
       </c>
       <c r="O28">
-        <v>68.489235776</v>
+        <v>66.841986752</v>
       </c>
       <c r="P28">
-        <v>145.539626024</v>
+        <v>142.039221848</v>
       </c>
       <c r="Q28">
-        <v>231.839626024</v>
+        <v>228.339221848</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.08814809163678822</v>
+        <v>0.08857836582325299</v>
       </c>
       <c r="T28">
-        <v>0.5519375975968568</v>
+        <v>0.5575455126552771</v>
       </c>
       <c r="U28">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V28">
         <v>0.32</v>
       </c>
       <c r="W28">
-        <v>0.037604</v>
+        <v>0.039304</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y28">
-        <v>4.551100380579838</v>
+        <v>4.19298483096097</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.07527428705097468</v>
+        <v>0.07509994629072606</v>
       </c>
       <c r="C29">
-        <v>3414.26628602984</v>
+        <v>3387.083152222067</v>
       </c>
       <c r="D29">
-        <v>4532.57928602984</v>
+        <v>4547.315152222067</v>
       </c>
       <c r="E29">
-        <v>59.01299999999992</v>
+        <v>100.932</v>
       </c>
       <c r="F29">
-        <v>1131.813</v>
+        <v>1173.732</v>
       </c>
       <c r="G29">
         <v>13.5</v>
@@ -3665,28 +3665,28 @@
         <v>274.3</v>
       </c>
       <c r="M29">
-        <v>65.4187914</v>
+        <v>67.8417096</v>
       </c>
       <c r="N29">
-        <v>208.8812086</v>
+        <v>206.4582904</v>
       </c>
       <c r="O29">
-        <v>66.841986752</v>
+        <v>66.06665292800001</v>
       </c>
       <c r="P29">
-        <v>142.039221848</v>
+        <v>140.391637472</v>
       </c>
       <c r="Q29">
-        <v>228.339221848</v>
+        <v>226.691637472</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.08857836582325299</v>
+        <v>0.08902059207045288</v>
       </c>
       <c r="T29">
-        <v>0.5575455126552771</v>
+        <v>0.5633092031319868</v>
       </c>
       <c r="U29">
         <v>0.0578</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>4.19298483096097</v>
+        <v>4.043235372712365</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.07509994629072606</v>
+        <v>0.07561580553047748</v>
       </c>
       <c r="C30">
-        <v>3387.083152222067</v>
+        <v>3301.837037781495</v>
       </c>
       <c r="D30">
-        <v>4547.315152222067</v>
+        <v>4503.988037781495</v>
       </c>
       <c r="E30">
-        <v>100.932</v>
+        <v>142.8510000000001</v>
       </c>
       <c r="F30">
-        <v>1173.732</v>
+        <v>1215.651</v>
       </c>
       <c r="G30">
         <v>13.5</v>
@@ -3747,45 +3747,45 @@
         <v>274.3</v>
       </c>
       <c r="M30">
-        <v>67.8417096</v>
+        <v>74.5194063</v>
       </c>
       <c r="N30">
-        <v>206.4582904</v>
+        <v>199.7805937</v>
       </c>
       <c r="O30">
-        <v>66.06665292800001</v>
+        <v>63.929789984</v>
       </c>
       <c r="P30">
-        <v>140.391637472</v>
+        <v>135.850803716</v>
       </c>
       <c r="Q30">
-        <v>226.691637472</v>
+        <v>222.150803716</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.08902059207045288</v>
+        <v>0.08947527539503869</v>
       </c>
       <c r="T30">
-        <v>0.5633092031319868</v>
+        <v>0.5692352510869138</v>
       </c>
       <c r="U30">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V30">
         <v>0.32</v>
       </c>
       <c r="W30">
-        <v>0.039304</v>
+        <v>0.041684</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y30">
-        <v>4.043235372712365</v>
+        <v>3.68092036181453</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.07561580553047748</v>
+        <v>0.07546526477022887</v>
       </c>
       <c r="C31">
-        <v>3301.837037781495</v>
+        <v>3272.476431155281</v>
       </c>
       <c r="D31">
-        <v>4503.988037781495</v>
+        <v>4516.546431155281</v>
       </c>
       <c r="E31">
-        <v>142.8509999999999</v>
+        <v>184.77</v>
       </c>
       <c r="F31">
-        <v>1215.651</v>
+        <v>1257.57</v>
       </c>
       <c r="G31">
         <v>13.5</v>
@@ -3829,28 +3829,28 @@
         <v>274.3</v>
       </c>
       <c r="M31">
-        <v>74.51940629999999</v>
+        <v>77.08904099999999</v>
       </c>
       <c r="N31">
-        <v>199.7805937</v>
+        <v>197.210959</v>
       </c>
       <c r="O31">
-        <v>63.92978998400001</v>
+        <v>63.10750688</v>
       </c>
       <c r="P31">
-        <v>135.850803716</v>
+        <v>134.10345212</v>
       </c>
       <c r="Q31">
-        <v>222.150803716</v>
+        <v>220.40345212</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.08947527539503869</v>
+        <v>0.08994294967175555</v>
       </c>
       <c r="T31">
-        <v>0.5692352510869138</v>
+        <v>0.5753306146976959</v>
       </c>
       <c r="U31">
         <v>0.0613</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>3.680920361814531</v>
+        <v>3.558223016420713</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.07546526477022887</v>
+        <v>0.07590496400998029</v>
       </c>
       <c r="C32">
-        <v>3272.476431155281</v>
+        <v>3194.071757623096</v>
       </c>
       <c r="D32">
-        <v>4516.546431155281</v>
+        <v>4480.060757623096</v>
       </c>
       <c r="E32">
-        <v>184.77</v>
+        <v>226.6889999999999</v>
       </c>
       <c r="F32">
-        <v>1257.57</v>
+        <v>1299.489</v>
       </c>
       <c r="G32">
         <v>13.5</v>
@@ -3911,45 +3911,45 @@
         <v>274.3</v>
       </c>
       <c r="M32">
-        <v>77.08904099999999</v>
+        <v>83.2972449</v>
       </c>
       <c r="N32">
-        <v>197.210959</v>
+        <v>191.0027551</v>
       </c>
       <c r="O32">
-        <v>63.10750688</v>
+        <v>61.120881632</v>
       </c>
       <c r="P32">
-        <v>134.10345212</v>
+        <v>129.881873468</v>
       </c>
       <c r="Q32">
-        <v>220.40345212</v>
+        <v>216.181873468</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.08994294967175555</v>
+        <v>0.09042417972460912</v>
       </c>
       <c r="T32">
-        <v>0.5753306146976959</v>
+        <v>0.5816026555145876</v>
       </c>
       <c r="U32">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V32">
         <v>0.32</v>
       </c>
       <c r="W32">
-        <v>0.041684</v>
+        <v>0.043588</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y32">
-        <v>3.558223016420713</v>
+        <v>3.293026081826627</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.07590496400998029</v>
+        <v>0.07577346324973169</v>
       </c>
       <c r="C33">
-        <v>3194.071757623096</v>
+        <v>3163.002585431309</v>
       </c>
       <c r="D33">
-        <v>4480.060757623096</v>
+        <v>4490.910585431309</v>
       </c>
       <c r="E33">
-        <v>226.6889999999999</v>
+        <v>268.6079999999999</v>
       </c>
       <c r="F33">
-        <v>1299.489</v>
+        <v>1341.408</v>
       </c>
       <c r="G33">
         <v>13.5</v>
@@ -3993,28 +3993,28 @@
         <v>274.3</v>
       </c>
       <c r="M33">
-        <v>83.2972449</v>
+        <v>85.98425279999999</v>
       </c>
       <c r="N33">
-        <v>191.0027551</v>
+        <v>188.3157472</v>
       </c>
       <c r="O33">
-        <v>61.120881632</v>
+        <v>60.26103910400001</v>
       </c>
       <c r="P33">
-        <v>129.881873468</v>
+        <v>128.054708096</v>
       </c>
       <c r="Q33">
-        <v>216.181873468</v>
+        <v>214.354708096</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.09042417972460912</v>
+        <v>0.0909195636025466</v>
       </c>
       <c r="T33">
-        <v>0.5816026555145876</v>
+        <v>0.5880591681202113</v>
       </c>
       <c r="U33">
         <v>0.0641</v>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>3.293026081826627</v>
+        <v>3.190119016769545</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.07577346324973169</v>
+        <v>0.07564196248948309</v>
       </c>
       <c r="C34">
-        <v>3163.002585431309</v>
+        <v>3131.986093126561</v>
       </c>
       <c r="D34">
-        <v>4490.910585431309</v>
+        <v>4501.813093126561</v>
       </c>
       <c r="E34">
-        <v>268.6079999999999</v>
+        <v>310.527</v>
       </c>
       <c r="F34">
-        <v>1341.408</v>
+        <v>1383.327</v>
       </c>
       <c r="G34">
         <v>13.5</v>
@@ -4075,28 +4075,28 @@
         <v>274.3</v>
       </c>
       <c r="M34">
-        <v>85.98425279999999</v>
+        <v>88.6712607</v>
       </c>
       <c r="N34">
-        <v>188.3157472</v>
+        <v>185.6287393</v>
       </c>
       <c r="O34">
-        <v>60.26103910400001</v>
+        <v>59.401196576</v>
       </c>
       <c r="P34">
-        <v>128.054708096</v>
+        <v>126.227542724</v>
       </c>
       <c r="Q34">
-        <v>214.354708096</v>
+        <v>212.527542724</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.0909195636025466</v>
+        <v>0.09142973505892998</v>
       </c>
       <c r="T34">
-        <v>0.5880591681202113</v>
+        <v>0.594708412445406</v>
       </c>
       <c r="U34">
         <v>0.0641</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>3.190119016769545</v>
+        <v>3.093448743534104</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.07564196248948309</v>
+        <v>0.07551046172923449</v>
       </c>
       <c r="C35">
-        <v>3131.986093126561</v>
+        <v>3101.022665312763</v>
       </c>
       <c r="D35">
-        <v>4501.813093126561</v>
+        <v>4512.768665312763</v>
       </c>
       <c r="E35">
-        <v>310.527</v>
+        <v>352.4459999999999</v>
       </c>
       <c r="F35">
-        <v>1383.327</v>
+        <v>1425.246</v>
       </c>
       <c r="G35">
         <v>13.5</v>
@@ -4157,28 +4157,28 @@
         <v>274.3</v>
       </c>
       <c r="M35">
-        <v>88.6712607</v>
+        <v>91.3582686</v>
       </c>
       <c r="N35">
-        <v>185.6287393</v>
+        <v>182.9417314</v>
       </c>
       <c r="O35">
-        <v>59.401196576</v>
+        <v>58.541354048</v>
       </c>
       <c r="P35">
-        <v>126.227542724</v>
+        <v>124.400377352</v>
       </c>
       <c r="Q35">
-        <v>212.527542724</v>
+        <v>210.700377352</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.09142973505892998</v>
+        <v>0.0919553662564159</v>
       </c>
       <c r="T35">
-        <v>0.594708412445406</v>
+        <v>0.6015591490228791</v>
       </c>
       <c r="U35">
         <v>0.0641</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>3.093448743534104</v>
+        <v>3.002464956959572</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.07551046172923449</v>
+        <v>0.07723536096898589</v>
       </c>
       <c r="C36">
-        <v>3101.022665312763</v>
+        <v>2919.505571256012</v>
       </c>
       <c r="D36">
-        <v>4512.768665312763</v>
+        <v>4373.170571256012</v>
       </c>
       <c r="E36">
-        <v>352.4459999999999</v>
+        <v>394.365</v>
       </c>
       <c r="F36">
-        <v>1425.246</v>
+        <v>1467.165</v>
       </c>
       <c r="G36">
         <v>13.5</v>
@@ -4239,45 +4239,45 @@
         <v>274.3</v>
       </c>
       <c r="M36">
-        <v>91.3582686</v>
+        <v>105.4891635</v>
       </c>
       <c r="N36">
-        <v>182.9417314</v>
+        <v>168.8108365</v>
       </c>
       <c r="O36">
-        <v>58.541354048</v>
+        <v>54.01946768</v>
       </c>
       <c r="P36">
-        <v>124.400377352</v>
+        <v>114.79136882</v>
       </c>
       <c r="Q36">
-        <v>210.700377352</v>
+        <v>201.09136882</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.0919553662564159</v>
+        <v>0.09249717072151677</v>
       </c>
       <c r="T36">
-        <v>0.6015591490228791</v>
+        <v>0.6086206774950439</v>
       </c>
       <c r="U36">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V36">
         <v>0.32</v>
       </c>
       <c r="W36">
-        <v>0.043588</v>
+        <v>0.048892</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y36">
-        <v>3.002464956959572</v>
+        <v>2.600267088097632</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.07723536096898589</v>
+        <v>0.07715690020873729</v>
       </c>
       <c r="C37">
-        <v>2919.505571256012</v>
+        <v>2883.748733691487</v>
       </c>
       <c r="D37">
-        <v>4373.170571256012</v>
+        <v>4379.332733691487</v>
       </c>
       <c r="E37">
-        <v>394.365</v>
+        <v>436.2840000000001</v>
       </c>
       <c r="F37">
-        <v>1467.165</v>
+        <v>1509.084</v>
       </c>
       <c r="G37">
         <v>13.5</v>
@@ -4321,28 +4321,28 @@
         <v>274.3</v>
       </c>
       <c r="M37">
-        <v>105.4891635</v>
+        <v>108.5031396</v>
       </c>
       <c r="N37">
-        <v>168.8108365</v>
+        <v>165.7968604</v>
       </c>
       <c r="O37">
-        <v>54.01946768</v>
+        <v>53.054995328</v>
       </c>
       <c r="P37">
-        <v>114.79136882</v>
+        <v>112.741865072</v>
       </c>
       <c r="Q37">
-        <v>201.09136882</v>
+        <v>199.041865072</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.09249717072151677</v>
+        <v>0.09305590657615202</v>
       </c>
       <c r="T37">
-        <v>0.6086206774950439</v>
+        <v>0.6159028787319637</v>
       </c>
       <c r="U37">
         <v>0.07190000000000001</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>2.600267088097632</v>
+        <v>2.528037446761586</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.07715690020873728</v>
+        <v>0.0780596794484887</v>
       </c>
       <c r="C38">
-        <v>2883.748733691488</v>
+        <v>2771.960024499406</v>
       </c>
       <c r="D38">
-        <v>4379.332733691488</v>
+        <v>4309.463024499406</v>
       </c>
       <c r="E38">
-        <v>436.2839999999999</v>
+        <v>478.203</v>
       </c>
       <c r="F38">
-        <v>1509.084</v>
+        <v>1551.003</v>
       </c>
       <c r="G38">
         <v>13.5</v>
@@ -4403,45 +4403,45 @@
         <v>274.3</v>
       </c>
       <c r="M38">
-        <v>108.5031396</v>
+        <v>117.5660274</v>
       </c>
       <c r="N38">
-        <v>165.7968604</v>
+        <v>156.7339726</v>
       </c>
       <c r="O38">
-        <v>53.054995328</v>
+        <v>50.154871232</v>
       </c>
       <c r="P38">
-        <v>112.741865072</v>
+        <v>106.579101368</v>
       </c>
       <c r="Q38">
-        <v>199.041865072</v>
+        <v>192.879101368</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.09305590657615201</v>
+        <v>0.09363238007696618</v>
       </c>
       <c r="T38">
-        <v>0.6159028787319636</v>
+        <v>0.6234162609605318</v>
       </c>
       <c r="U38">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V38">
         <v>0.32</v>
       </c>
       <c r="W38">
-        <v>0.048892</v>
+        <v>0.051544</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y38">
-        <v>2.528037446761587</v>
+        <v>2.333157001781962</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.0780596794484887</v>
+        <v>0.0780077386882401</v>
       </c>
       <c r="C39">
-        <v>2771.960024499406</v>
+        <v>2734.000427637502</v>
       </c>
       <c r="D39">
-        <v>4309.463024499406</v>
+        <v>4313.422427637502</v>
       </c>
       <c r="E39">
-        <v>478.203</v>
+        <v>520.1219999999998</v>
       </c>
       <c r="F39">
-        <v>1551.003</v>
+        <v>1592.922</v>
       </c>
       <c r="G39">
         <v>13.5</v>
@@ -4485,28 +4485,28 @@
         <v>274.3</v>
       </c>
       <c r="M39">
-        <v>117.5660274</v>
+        <v>120.7434876</v>
       </c>
       <c r="N39">
-        <v>156.7339726</v>
+        <v>153.5565124</v>
       </c>
       <c r="O39">
-        <v>50.154871232</v>
+        <v>49.13808396800001</v>
       </c>
       <c r="P39">
-        <v>106.579101368</v>
+        <v>104.418428432</v>
       </c>
       <c r="Q39">
-        <v>192.879101368</v>
+        <v>190.718428432</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.09363238007696618</v>
+        <v>0.09422744949716144</v>
       </c>
       <c r="T39">
-        <v>0.6234162609605318</v>
+        <v>0.6311720103577634</v>
       </c>
       <c r="U39">
         <v>0.07580000000000001</v>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>2.333157001781962</v>
+        <v>2.271758133314016</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.0780077386882401</v>
+        <v>0.0779557979279915</v>
       </c>
       <c r="C40">
-        <v>2734.000427637502</v>
+        <v>2696.048113023895</v>
       </c>
       <c r="D40">
-        <v>4313.422427637502</v>
+        <v>4317.389113023895</v>
       </c>
       <c r="E40">
-        <v>520.1219999999998</v>
+        <v>562.0409999999999</v>
       </c>
       <c r="F40">
-        <v>1592.922</v>
+        <v>1634.841</v>
       </c>
       <c r="G40">
         <v>13.5</v>
@@ -4567,28 +4567,28 @@
         <v>274.3</v>
       </c>
       <c r="M40">
-        <v>120.7434876</v>
+        <v>123.9209478</v>
       </c>
       <c r="N40">
-        <v>153.5565124</v>
+        <v>150.3790522</v>
       </c>
       <c r="O40">
-        <v>49.13808396800001</v>
+        <v>48.121296704</v>
       </c>
       <c r="P40">
-        <v>104.418428432</v>
+        <v>102.257755496</v>
       </c>
       <c r="Q40">
-        <v>190.718428432</v>
+        <v>188.557755496</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.09422744949716144</v>
+        <v>0.09484202939014999</v>
       </c>
       <c r="T40">
-        <v>0.6311720103577634</v>
+        <v>0.639182046620478</v>
       </c>
       <c r="U40">
         <v>0.07580000000000001</v>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>2.271758133314016</v>
+        <v>2.213507924767502</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.0779557979279915</v>
+        <v>0.0779038571677429</v>
       </c>
       <c r="C41">
-        <v>2696.048113023895</v>
+        <v>2658.103100767662</v>
       </c>
       <c r="D41">
-        <v>4317.389113023895</v>
+        <v>4321.363100767662</v>
       </c>
       <c r="E41">
-        <v>562.0409999999999</v>
+        <v>603.96</v>
       </c>
       <c r="F41">
-        <v>1634.841</v>
+        <v>1676.76</v>
       </c>
       <c r="G41">
         <v>13.5</v>
@@ -4649,28 +4649,28 @@
         <v>274.3</v>
       </c>
       <c r="M41">
-        <v>123.9209478</v>
+        <v>127.098408</v>
       </c>
       <c r="N41">
-        <v>150.3790522</v>
+        <v>147.201592</v>
       </c>
       <c r="O41">
-        <v>48.121296704</v>
+        <v>47.10450944</v>
       </c>
       <c r="P41">
-        <v>102.257755496</v>
+        <v>100.09708256</v>
       </c>
       <c r="Q41">
-        <v>188.557755496</v>
+        <v>186.39708256</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.09484202939014999</v>
+        <v>0.0954770952795715</v>
       </c>
       <c r="T41">
-        <v>0.639182046620478</v>
+        <v>0.6474590840919497</v>
       </c>
       <c r="U41">
         <v>0.07580000000000001</v>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>2.213507924767502</v>
+        <v>2.158170226648315</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.0779038571677429</v>
+        <v>0.0778519164074943</v>
       </c>
       <c r="C42">
-        <v>2658.103100767662</v>
+        <v>2620.165411051981</v>
       </c>
       <c r="D42">
-        <v>4321.363100767662</v>
+        <v>4325.344411051981</v>
       </c>
       <c r="E42">
-        <v>603.96</v>
+        <v>645.8790000000001</v>
       </c>
       <c r="F42">
-        <v>1676.76</v>
+        <v>1718.679</v>
       </c>
       <c r="G42">
         <v>13.5</v>
@@ -4731,28 +4731,28 @@
         <v>274.3</v>
       </c>
       <c r="M42">
-        <v>127.098408</v>
+        <v>130.2758682</v>
       </c>
       <c r="N42">
-        <v>147.201592</v>
+        <v>144.0241318</v>
       </c>
       <c r="O42">
-        <v>47.10450944</v>
+        <v>46.087722176</v>
       </c>
       <c r="P42">
-        <v>100.09708256</v>
+        <v>97.93640962399999</v>
       </c>
       <c r="Q42">
-        <v>186.39708256</v>
+        <v>184.236409624</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.0954770952795715</v>
+        <v>0.09613368882626153</v>
       </c>
       <c r="T42">
-        <v>0.6474590840919497</v>
+        <v>0.6560166991048273</v>
       </c>
       <c r="U42">
         <v>0.07580000000000001</v>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>2.158170226648315</v>
+        <v>2.10553192843738</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.0778519164074943</v>
+        <v>0.07779997564724571</v>
       </c>
       <c r="C43">
-        <v>2620.165411051981</v>
+        <v>2582.235064134481</v>
       </c>
       <c r="D43">
-        <v>4325.344411051981</v>
+        <v>4329.333064134481</v>
       </c>
       <c r="E43">
-        <v>645.8790000000001</v>
+        <v>687.798</v>
       </c>
       <c r="F43">
-        <v>1718.679</v>
+        <v>1760.598</v>
       </c>
       <c r="G43">
         <v>13.5</v>
@@ -4813,28 +4813,28 @@
         <v>274.3</v>
       </c>
       <c r="M43">
-        <v>130.2758682</v>
+        <v>133.4533284</v>
       </c>
       <c r="N43">
-        <v>144.0241318</v>
+        <v>140.8466716</v>
       </c>
       <c r="O43">
-        <v>46.087722176</v>
+        <v>45.07093491200001</v>
       </c>
       <c r="P43">
-        <v>97.93640962399999</v>
+        <v>95.77573668799999</v>
       </c>
       <c r="Q43">
-        <v>184.236409624</v>
+        <v>182.075736688</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.09613368882626153</v>
+        <v>0.09681292352973397</v>
       </c>
       <c r="T43">
-        <v>0.6560166991048273</v>
+        <v>0.6648694042905627</v>
       </c>
       <c r="U43">
         <v>0.07580000000000001</v>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>2.10553192843738</v>
+        <v>2.055400215855538</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.07779997564724571</v>
+        <v>0.07774803488699712</v>
       </c>
       <c r="C44">
-        <v>2582.235064134481</v>
+        <v>2544.312080347583</v>
       </c>
       <c r="D44">
-        <v>4329.333064134481</v>
+        <v>4333.329080347583</v>
       </c>
       <c r="E44">
-        <v>687.7979999999998</v>
+        <v>729.7169999999999</v>
       </c>
       <c r="F44">
-        <v>1760.598</v>
+        <v>1802.517</v>
       </c>
       <c r="G44">
         <v>13.5</v>
@@ -4895,28 +4895,28 @@
         <v>274.3</v>
       </c>
       <c r="M44">
-        <v>133.4533284</v>
+        <v>136.6307886</v>
       </c>
       <c r="N44">
-        <v>140.8466716</v>
+        <v>137.6692114</v>
       </c>
       <c r="O44">
-        <v>45.07093491200001</v>
+        <v>44.05414764800001</v>
       </c>
       <c r="P44">
-        <v>95.77573668799999</v>
+        <v>93.61506375200001</v>
       </c>
       <c r="Q44">
-        <v>182.075736688</v>
+        <v>179.915063752</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.09681292352973397</v>
+        <v>0.09751599102981949</v>
       </c>
       <c r="T44">
-        <v>0.6648694042905627</v>
+        <v>0.6740327307108854</v>
       </c>
       <c r="U44">
         <v>0.07580000000000001</v>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>2.055400215855538</v>
+        <v>2.007600210835642</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.07774803488699712</v>
+        <v>0.08194473412674852</v>
       </c>
       <c r="C45">
-        <v>2544.312080347583</v>
+        <v>2201.654007041951</v>
       </c>
       <c r="D45">
-        <v>4333.329080347583</v>
+        <v>4032.590007041951</v>
       </c>
       <c r="E45">
-        <v>729.7169999999999</v>
+        <v>771.636</v>
       </c>
       <c r="F45">
-        <v>1802.517</v>
+        <v>1844.436</v>
       </c>
       <c r="G45">
         <v>13.5</v>
@@ -4977,45 +4977,45 @@
         <v>274.3</v>
       </c>
       <c r="M45">
-        <v>136.6307886</v>
+        <v>165.99924</v>
       </c>
       <c r="N45">
-        <v>137.6692114</v>
+        <v>108.30076</v>
       </c>
       <c r="O45">
-        <v>44.05414764800001</v>
+        <v>34.65624320000001</v>
       </c>
       <c r="P45">
-        <v>93.61506375200001</v>
+        <v>73.64451680000002</v>
       </c>
       <c r="Q45">
-        <v>179.915063752</v>
+        <v>159.9445168</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.09751599102981949</v>
+        <v>0.09824416808347949</v>
       </c>
       <c r="T45">
-        <v>0.6740327307108854</v>
+        <v>0.6835233187890767</v>
       </c>
       <c r="U45">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V45">
         <v>0.32</v>
       </c>
       <c r="W45">
-        <v>0.051544</v>
+        <v>0.06119999999999999</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y45">
-        <v>2.007600210835642</v>
+        <v>1.652417203837801</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.08194473412674852</v>
+        <v>0.0819893533664999</v>
       </c>
       <c r="C46">
-        <v>2201.654007041951</v>
+        <v>2156.761655640256</v>
       </c>
       <c r="D46">
-        <v>4032.590007041951</v>
+        <v>4029.616655640256</v>
       </c>
       <c r="E46">
-        <v>771.636</v>
+        <v>813.5549999999998</v>
       </c>
       <c r="F46">
-        <v>1844.436</v>
+        <v>1886.355</v>
       </c>
       <c r="G46">
         <v>13.5</v>
@@ -5059,28 +5059,28 @@
         <v>274.3</v>
       </c>
       <c r="M46">
-        <v>165.99924</v>
+        <v>169.77195</v>
       </c>
       <c r="N46">
-        <v>108.30076</v>
+        <v>104.52805</v>
       </c>
       <c r="O46">
-        <v>34.65624320000001</v>
+        <v>33.44897600000001</v>
       </c>
       <c r="P46">
-        <v>73.64451680000002</v>
+        <v>71.07907400000002</v>
       </c>
       <c r="Q46">
-        <v>159.9445168</v>
+        <v>157.379074</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.09824416808347949</v>
+        <v>0.09899882430272711</v>
       </c>
       <c r="T46">
-        <v>0.6835233187890767</v>
+        <v>0.6933590191610204</v>
       </c>
       <c r="U46">
         <v>0.09</v>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>1.652417203837801</v>
+        <v>1.615696821530294</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.0819893533664999</v>
+        <v>0.08203397260625132</v>
       </c>
       <c r="C47">
-        <v>2156.761655640256</v>
+        <v>2111.87368569303</v>
       </c>
       <c r="D47">
-        <v>4029.616655640256</v>
+        <v>4026.647685693029</v>
       </c>
       <c r="E47">
-        <v>813.5549999999998</v>
+        <v>855.4739999999999</v>
       </c>
       <c r="F47">
-        <v>1886.355</v>
+        <v>1928.274</v>
       </c>
       <c r="G47">
         <v>13.5</v>
@@ -5141,28 +5141,28 @@
         <v>274.3</v>
       </c>
       <c r="M47">
-        <v>169.77195</v>
+        <v>173.54466</v>
       </c>
       <c r="N47">
-        <v>104.52805</v>
+        <v>100.75534</v>
       </c>
       <c r="O47">
-        <v>33.44897600000001</v>
+        <v>32.2417088</v>
       </c>
       <c r="P47">
-        <v>71.07907400000002</v>
+        <v>68.51363120000002</v>
       </c>
       <c r="Q47">
-        <v>157.379074</v>
+        <v>154.8136312</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.09899882430272711</v>
+        <v>0.09978143075231727</v>
       </c>
       <c r="T47">
-        <v>0.6933590191610204</v>
+        <v>0.7035590047319251</v>
       </c>
       <c r="U47">
         <v>0.09</v>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>1.615696821530294</v>
+        <v>1.580572977583983</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.08203397260625132</v>
+        <v>0.08207859184600272</v>
       </c>
       <c r="C48">
-        <v>2111.87368569303</v>
+        <v>2066.990087522805</v>
       </c>
       <c r="D48">
-        <v>4026.647685693029</v>
+        <v>4023.683087522805</v>
       </c>
       <c r="E48">
-        <v>855.4739999999999</v>
+        <v>897.393</v>
       </c>
       <c r="F48">
-        <v>1928.274</v>
+        <v>1970.193</v>
       </c>
       <c r="G48">
         <v>13.5</v>
@@ -5223,28 +5223,28 @@
         <v>274.3</v>
       </c>
       <c r="M48">
-        <v>173.54466</v>
+        <v>177.31737</v>
       </c>
       <c r="N48">
-        <v>100.75534</v>
+        <v>96.98263000000003</v>
       </c>
       <c r="O48">
-        <v>32.2417088</v>
+        <v>31.03444160000001</v>
       </c>
       <c r="P48">
-        <v>68.51363120000002</v>
+        <v>65.94818840000002</v>
       </c>
       <c r="Q48">
-        <v>154.8136312</v>
+        <v>152.2481884</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.09978143075231727</v>
+        <v>0.1005935695207598</v>
       </c>
       <c r="T48">
-        <v>0.7035590047319251</v>
+        <v>0.7141438954187128</v>
       </c>
       <c r="U48">
         <v>0.09</v>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>1.580572977583983</v>
+        <v>1.546943765294963</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.08207859184600272</v>
+        <v>0.08212321108575413</v>
       </c>
       <c r="C49">
-        <v>2066.990087522805</v>
+        <v>2022.110851480593</v>
       </c>
       <c r="D49">
-        <v>4023.683087522805</v>
+        <v>4020.722851480593</v>
       </c>
       <c r="E49">
-        <v>897.393</v>
+        <v>939.3120000000001</v>
       </c>
       <c r="F49">
-        <v>1970.193</v>
+        <v>2012.112</v>
       </c>
       <c r="G49">
         <v>13.5</v>
@@ -5305,28 +5305,28 @@
         <v>274.3</v>
       </c>
       <c r="M49">
-        <v>177.31737</v>
+        <v>181.09008</v>
       </c>
       <c r="N49">
-        <v>96.98263000000003</v>
+        <v>93.20992000000001</v>
       </c>
       <c r="O49">
-        <v>31.03444160000001</v>
+        <v>29.8271744</v>
       </c>
       <c r="P49">
-        <v>65.94818840000002</v>
+        <v>63.38274560000001</v>
       </c>
       <c r="Q49">
-        <v>152.2481884</v>
+        <v>149.6827456</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1005935695207598</v>
+        <v>0.101436944395681</v>
       </c>
       <c r="T49">
-        <v>0.7141438954187128</v>
+        <v>0.7251358972857617</v>
       </c>
       <c r="U49">
         <v>0.09</v>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>1.546943765294963</v>
+        <v>1.514715770184651</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.08212321108575411</v>
+        <v>0.1036564376016187</v>
       </c>
       <c r="C50">
-        <v>2022.110851480594</v>
+        <v>926.6826460591101</v>
       </c>
       <c r="D50">
-        <v>4020.722851480594</v>
+        <v>2967.21364605911</v>
       </c>
       <c r="E50">
-        <v>939.3119999999999</v>
+        <v>981.231</v>
       </c>
       <c r="F50">
-        <v>2012.112</v>
+        <v>2054.031</v>
       </c>
       <c r="G50">
         <v>13.5</v>
@@ -5387,45 +5387,45 @@
         <v>274.3</v>
       </c>
       <c r="M50">
-        <v>181.09008</v>
+        <v>301.5317508</v>
       </c>
       <c r="N50">
-        <v>93.20992000000004</v>
+        <v>-27.23175079999999</v>
       </c>
       <c r="O50">
-        <v>29.82717440000001</v>
+        <v>-8.714160255999996</v>
       </c>
       <c r="P50">
-        <v>63.38274560000002</v>
+        <v>-18.51759054399999</v>
       </c>
       <c r="Q50">
-        <v>149.6827456</v>
+        <v>67.78240945600001</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.101436944395681</v>
+        <v>0.1032624870757868</v>
       </c>
       <c r="T50">
-        <v>0.7251358972857616</v>
+        <v>0.7489288381769357</v>
       </c>
       <c r="U50">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V50">
-        <v>0.32</v>
+        <v>0.2911003559894429</v>
       </c>
       <c r="W50">
-        <v>0.06119999999999999</v>
+        <v>0.1040664677407498</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y50">
-        <v>1.514715770184651</v>
+        <v>0.9096886124670093</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1036564376016187</v>
+        <v>0.1046664376016186</v>
       </c>
       <c r="C51">
-        <v>926.6826460591101</v>
+        <v>848.7397734462838</v>
       </c>
       <c r="D51">
-        <v>2967.21364605911</v>
+        <v>2931.189773446284</v>
       </c>
       <c r="E51">
-        <v>981.231</v>
+        <v>1023.15</v>
       </c>
       <c r="F51">
-        <v>2054.031</v>
+        <v>2095.95</v>
       </c>
       <c r="G51">
         <v>13.5</v>
@@ -5469,37 +5469,37 @@
         <v>274.3</v>
       </c>
       <c r="M51">
-        <v>301.5317508</v>
+        <v>307.68546</v>
       </c>
       <c r="N51">
-        <v>-27.23175079999999</v>
+        <v>-33.38545999999997</v>
       </c>
       <c r="O51">
-        <v>-8.714160255999996</v>
+        <v>-10.68334719999999</v>
       </c>
       <c r="P51">
-        <v>-18.51759054399999</v>
+        <v>-22.70211279999998</v>
       </c>
       <c r="Q51">
-        <v>67.78240945600001</v>
+        <v>63.59788720000002</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1032624870757868</v>
+        <v>0.1044117368173025</v>
       </c>
       <c r="T51">
-        <v>0.7489288381769357</v>
+        <v>0.7639074149404744</v>
       </c>
       <c r="U51">
         <v>0.1468</v>
       </c>
       <c r="V51">
-        <v>0.2911003559894429</v>
+        <v>0.2852783488696541</v>
       </c>
       <c r="W51">
-        <v>0.1040664677407498</v>
+        <v>0.1049211383859348</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.9096886124670093</v>
+        <v>0.8914948402176691</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1046664376016186</v>
+        <v>0.1056764376016187</v>
       </c>
       <c r="C52">
-        <v>848.7397734462838</v>
+        <v>771.6611144628869</v>
       </c>
       <c r="D52">
-        <v>2931.189773446284</v>
+        <v>2896.030114462887</v>
       </c>
       <c r="E52">
-        <v>1023.15</v>
+        <v>1065.069</v>
       </c>
       <c r="F52">
-        <v>2095.95</v>
+        <v>2137.869</v>
       </c>
       <c r="G52">
         <v>13.5</v>
@@ -5551,37 +5551,37 @@
         <v>274.3</v>
       </c>
       <c r="M52">
-        <v>307.68546</v>
+        <v>313.8391692</v>
       </c>
       <c r="N52">
-        <v>-33.38545999999997</v>
+        <v>-39.53916919999995</v>
       </c>
       <c r="O52">
-        <v>-10.68334719999999</v>
+        <v>-12.65253414399998</v>
       </c>
       <c r="P52">
-        <v>-22.70211279999998</v>
+        <v>-26.88663505599996</v>
       </c>
       <c r="Q52">
-        <v>63.59788720000002</v>
+        <v>59.41336494400004</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1044117368173025</v>
+        <v>0.1056078947115332</v>
       </c>
       <c r="T52">
-        <v>0.7639074149404744</v>
+        <v>0.7794973621841577</v>
       </c>
       <c r="U52">
         <v>0.1468</v>
       </c>
       <c r="V52">
-        <v>0.2852783488696541</v>
+        <v>0.2796846557545629</v>
       </c>
       <c r="W52">
-        <v>0.1049211383859348</v>
+        <v>0.1057422925352302</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.8914948402176691</v>
+        <v>0.874014549233009</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1056764376016187</v>
+        <v>0.1066864376016187</v>
       </c>
       <c r="C53">
-        <v>771.6611144628869</v>
+        <v>695.4159389567326</v>
       </c>
       <c r="D53">
-        <v>2896.030114462887</v>
+        <v>2861.703938956733</v>
       </c>
       <c r="E53">
-        <v>1065.069</v>
+        <v>1106.988</v>
       </c>
       <c r="F53">
-        <v>2137.869</v>
+        <v>2179.788</v>
       </c>
       <c r="G53">
         <v>13.5</v>
@@ -5633,37 +5633,37 @@
         <v>274.3</v>
       </c>
       <c r="M53">
-        <v>313.8391692</v>
+        <v>319.9928784000001</v>
       </c>
       <c r="N53">
-        <v>-39.53916919999995</v>
+        <v>-45.69287840000004</v>
       </c>
       <c r="O53">
-        <v>-12.65253414399998</v>
+        <v>-14.62172108800001</v>
       </c>
       <c r="P53">
-        <v>-26.88663505599996</v>
+        <v>-31.07115731200003</v>
       </c>
       <c r="Q53">
-        <v>59.41336494400004</v>
+        <v>55.22884268799997</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1056078947115332</v>
+        <v>0.1068538925180235</v>
       </c>
       <c r="T53">
-        <v>0.7794973621841577</v>
+        <v>0.7957368905629943</v>
       </c>
       <c r="U53">
         <v>0.1468</v>
       </c>
       <c r="V53">
-        <v>0.2796846557545629</v>
+        <v>0.2743061046823597</v>
       </c>
       <c r="W53">
-        <v>0.1057422925352302</v>
+        <v>0.1065318638326296</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.874014549233009</v>
+        <v>0.857206577132374</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1066864376016187</v>
+        <v>0.1076964376016187</v>
       </c>
       <c r="C54">
-        <v>695.4159389567326</v>
+        <v>619.9749566668861</v>
       </c>
       <c r="D54">
-        <v>2861.703938956733</v>
+        <v>2828.181956666886</v>
       </c>
       <c r="E54">
-        <v>1106.988</v>
+        <v>1148.907</v>
       </c>
       <c r="F54">
-        <v>2179.788</v>
+        <v>2221.707</v>
       </c>
       <c r="G54">
         <v>13.5</v>
@@ -5715,37 +5715,37 @@
         <v>274.3</v>
       </c>
       <c r="M54">
-        <v>319.9928784000001</v>
+        <v>326.1465876</v>
       </c>
       <c r="N54">
-        <v>-45.69287840000004</v>
+        <v>-51.84658760000002</v>
       </c>
       <c r="O54">
-        <v>-14.62172108800001</v>
+        <v>-16.59090803200001</v>
       </c>
       <c r="P54">
-        <v>-31.07115731200003</v>
+        <v>-35.25567956800001</v>
       </c>
       <c r="Q54">
-        <v>55.22884268799997</v>
+        <v>51.04432043199999</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1068538925180235</v>
+        <v>0.1081529115077687</v>
       </c>
       <c r="T54">
-        <v>0.7957368905629943</v>
+        <v>0.8126674627026326</v>
       </c>
       <c r="U54">
         <v>0.1468</v>
       </c>
       <c r="V54">
-        <v>0.2743061046823597</v>
+        <v>0.2691305178015604</v>
       </c>
       <c r="W54">
-        <v>0.1065318638326296</v>
+        <v>0.1072916399867309</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.857206577132374</v>
+        <v>0.8410328681298764</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1076964376016187</v>
+        <v>0.1087064376016187</v>
       </c>
       <c r="C55">
-        <v>619.9749566668861</v>
+        <v>545.310233865735</v>
       </c>
       <c r="D55">
-        <v>2828.181956666886</v>
+        <v>2795.436233865735</v>
       </c>
       <c r="E55">
-        <v>1148.907</v>
+        <v>1190.826</v>
       </c>
       <c r="F55">
-        <v>2221.707</v>
+        <v>2263.626</v>
       </c>
       <c r="G55">
         <v>13.5</v>
@@ -5797,37 +5797,37 @@
         <v>274.3</v>
       </c>
       <c r="M55">
-        <v>326.1465876</v>
+        <v>332.3002968</v>
       </c>
       <c r="N55">
-        <v>-51.84658760000002</v>
+        <v>-58.0002968</v>
       </c>
       <c r="O55">
-        <v>-16.59090803200001</v>
+        <v>-18.560094976</v>
       </c>
       <c r="P55">
-        <v>-35.25567956800001</v>
+        <v>-39.440201824</v>
       </c>
       <c r="Q55">
-        <v>51.04432043199999</v>
+        <v>46.859798176</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1081529115077687</v>
+        <v>0.1095084095840245</v>
       </c>
       <c r="T55">
-        <v>0.8126674627026326</v>
+        <v>0.8303341466744288</v>
       </c>
       <c r="U55">
         <v>0.1468</v>
       </c>
       <c r="V55">
-        <v>0.2691305178015604</v>
+        <v>0.2641466193237538</v>
       </c>
       <c r="W55">
-        <v>0.1072916399867309</v>
+        <v>0.1080232762832729</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.8410328681298764</v>
+        <v>0.8254581853867307</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1087064376016187</v>
+        <v>0.1097164376016187</v>
       </c>
       <c r="C56">
-        <v>545.310233865735</v>
+        <v>471.3951157256611</v>
       </c>
       <c r="D56">
-        <v>2795.436233865735</v>
+        <v>2763.440115725661</v>
       </c>
       <c r="E56">
-        <v>1190.826</v>
+        <v>1232.745</v>
       </c>
       <c r="F56">
-        <v>2263.626</v>
+        <v>2305.545</v>
       </c>
       <c r="G56">
         <v>13.5</v>
@@ -5879,37 +5879,37 @@
         <v>274.3</v>
       </c>
       <c r="M56">
-        <v>332.3002968</v>
+        <v>338.454006</v>
       </c>
       <c r="N56">
-        <v>-58.0002968</v>
+        <v>-64.15400600000004</v>
       </c>
       <c r="O56">
-        <v>-18.560094976</v>
+        <v>-20.52928192000001</v>
       </c>
       <c r="P56">
-        <v>-39.440201824</v>
+        <v>-43.62472408000002</v>
       </c>
       <c r="Q56">
-        <v>46.859798176</v>
+        <v>42.67527591999998</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1095084095840245</v>
+        <v>0.1109241520192251</v>
       </c>
       <c r="T56">
-        <v>0.8303341466744288</v>
+        <v>0.8487860166005273</v>
       </c>
       <c r="U56">
         <v>0.1468</v>
       </c>
       <c r="V56">
-        <v>0.2641466193237538</v>
+        <v>0.2593439535178673</v>
       </c>
       <c r="W56">
-        <v>0.1080232762832729</v>
+        <v>0.1087283076235771</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.8254581853867307</v>
+        <v>0.8104498547433354</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1097164376016187</v>
+        <v>0.1422776100873155</v>
       </c>
       <c r="C57">
-        <v>471.3951157256611</v>
+        <v>-315.3810038654451</v>
       </c>
       <c r="D57">
-        <v>2763.440115725661</v>
+        <v>2018.582996134555</v>
       </c>
       <c r="E57">
-        <v>1232.745</v>
+        <v>1274.664</v>
       </c>
       <c r="F57">
-        <v>2305.545</v>
+        <v>2347.464</v>
       </c>
       <c r="G57">
         <v>13.5</v>
@@ -5961,45 +5961,45 @@
         <v>274.3</v>
       </c>
       <c r="M57">
-        <v>338.454006</v>
+        <v>471.3707712</v>
       </c>
       <c r="N57">
-        <v>-64.15400600000004</v>
+        <v>-197.0707712</v>
       </c>
       <c r="O57">
-        <v>-20.52928192000001</v>
+        <v>-63.06264678399999</v>
       </c>
       <c r="P57">
-        <v>-43.62472408000002</v>
+        <v>-134.008124416</v>
       </c>
       <c r="Q57">
-        <v>42.67527591999998</v>
+        <v>-47.70812441599999</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1109241520192251</v>
+        <v>0.1153841838507911</v>
       </c>
       <c r="T57">
-        <v>0.8487860166005273</v>
+        <v>0.9069151827370623</v>
       </c>
       <c r="U57">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V57">
-        <v>0.2593439535178673</v>
+        <v>0.1862143462492229</v>
       </c>
       <c r="W57">
-        <v>0.1087283076235771</v>
+        <v>0.1634081592731561</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y57">
-        <v>0.8104498547433354</v>
+        <v>0.5819198320288215</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1422776100873155</v>
+        <v>0.1438276100873155</v>
       </c>
       <c r="C58">
-        <v>-315.3810038654451</v>
+        <v>-382.8719793243195</v>
       </c>
       <c r="D58">
-        <v>2018.582996134555</v>
+        <v>1993.011020675681</v>
       </c>
       <c r="E58">
-        <v>1274.664</v>
+        <v>1316.583</v>
       </c>
       <c r="F58">
-        <v>2347.464</v>
+        <v>2389.383</v>
       </c>
       <c r="G58">
         <v>13.5</v>
@@ -6043,37 +6043,37 @@
         <v>274.3</v>
       </c>
       <c r="M58">
-        <v>471.3707712</v>
+        <v>479.7881064000001</v>
       </c>
       <c r="N58">
-        <v>-197.0707712</v>
+        <v>-205.4881064</v>
       </c>
       <c r="O58">
-        <v>-63.06264678399999</v>
+        <v>-65.75619404800001</v>
       </c>
       <c r="P58">
-        <v>-134.008124416</v>
+        <v>-139.7319123520001</v>
       </c>
       <c r="Q58">
-        <v>-47.70812441599999</v>
+        <v>-53.43191235200005</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1153841838507911</v>
+        <v>0.1170024206845304</v>
       </c>
       <c r="T58">
-        <v>0.9069151827370623</v>
+        <v>0.9280062334983893</v>
       </c>
       <c r="U58">
         <v>0.2008</v>
       </c>
       <c r="V58">
-        <v>0.1862143462492229</v>
+        <v>0.1829474278939733</v>
       </c>
       <c r="W58">
-        <v>0.1634081592731561</v>
+        <v>0.1640641564788902</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.5819198320288215</v>
+        <v>0.5717107121686666</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1438276100873155</v>
+        <v>0.1453776100873155</v>
       </c>
       <c r="C59">
-        <v>-382.8719793243195</v>
+        <v>-449.7231540460114</v>
       </c>
       <c r="D59">
-        <v>1993.011020675681</v>
+        <v>1968.078845953989</v>
       </c>
       <c r="E59">
-        <v>1316.583</v>
+        <v>1358.502</v>
       </c>
       <c r="F59">
-        <v>2389.383</v>
+        <v>2431.302</v>
       </c>
       <c r="G59">
         <v>13.5</v>
@@ -6125,37 +6125,37 @@
         <v>274.3</v>
       </c>
       <c r="M59">
-        <v>479.7881064000001</v>
+        <v>488.2054416</v>
       </c>
       <c r="N59">
-        <v>-205.4881064</v>
+        <v>-213.9054416</v>
       </c>
       <c r="O59">
-        <v>-65.75619404800001</v>
+        <v>-68.449741312</v>
       </c>
       <c r="P59">
-        <v>-139.7319123520001</v>
+        <v>-145.455700288</v>
       </c>
       <c r="Q59">
-        <v>-53.43191235200005</v>
+        <v>-59.15570028800001</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1170024206845304</v>
+        <v>0.1186977164151145</v>
       </c>
       <c r="T59">
-        <v>0.9280062334983893</v>
+        <v>0.950101620010256</v>
       </c>
       <c r="U59">
         <v>0.2008</v>
       </c>
       <c r="V59">
-        <v>0.1829474278939733</v>
+        <v>0.1797931618958014</v>
       </c>
       <c r="W59">
-        <v>0.1640641564788902</v>
+        <v>0.1646975330913231</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.5717107121686666</v>
+        <v>0.5618536309243793</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1453776100873155</v>
+        <v>0.1469276100873154</v>
       </c>
       <c r="C60">
-        <v>-449.7231540460109</v>
+        <v>-515.9582427076289</v>
       </c>
       <c r="D60">
-        <v>1968.078845953989</v>
+        <v>1943.762757292371</v>
       </c>
       <c r="E60">
-        <v>1358.502</v>
+        <v>1400.421</v>
       </c>
       <c r="F60">
-        <v>2431.302</v>
+        <v>2473.221</v>
       </c>
       <c r="G60">
         <v>13.5</v>
@@ -6207,37 +6207,37 @@
         <v>274.3</v>
       </c>
       <c r="M60">
-        <v>488.2054416</v>
+        <v>496.6227767999999</v>
       </c>
       <c r="N60">
-        <v>-213.9054416</v>
+        <v>-222.3227767999999</v>
       </c>
       <c r="O60">
-        <v>-68.44974131199999</v>
+        <v>-71.14328857599997</v>
       </c>
       <c r="P60">
-        <v>-145.455700288</v>
+        <v>-151.179488224</v>
       </c>
       <c r="Q60">
-        <v>-59.15570028799998</v>
+        <v>-64.87948822399996</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1186977164151145</v>
+        <v>0.1204757094984099</v>
       </c>
       <c r="T60">
-        <v>0.9501016200102556</v>
+        <v>0.9732748302544082</v>
       </c>
       <c r="U60">
         <v>0.2008</v>
       </c>
       <c r="V60">
-        <v>0.1797931618958014</v>
+        <v>0.1767458201687539</v>
       </c>
       <c r="W60">
-        <v>0.1646975330913231</v>
+        <v>0.1653094393101142</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.5618536309243793</v>
+        <v>0.552330688027356</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1469276100873154</v>
+        <v>0.1484776100873155</v>
       </c>
       <c r="C61">
-        <v>-515.9582427076289</v>
+        <v>-581.5998022877118</v>
       </c>
       <c r="D61">
-        <v>1943.762757292371</v>
+        <v>1920.040197712288</v>
       </c>
       <c r="E61">
-        <v>1400.421</v>
+        <v>1442.34</v>
       </c>
       <c r="F61">
-        <v>2473.221</v>
+        <v>2515.14</v>
       </c>
       <c r="G61">
         <v>13.5</v>
@@ -6289,37 +6289,37 @@
         <v>274.3</v>
       </c>
       <c r="M61">
-        <v>496.6227767999999</v>
+        <v>505.040112</v>
       </c>
       <c r="N61">
-        <v>-222.3227767999999</v>
+        <v>-230.740112</v>
       </c>
       <c r="O61">
-        <v>-71.14328857599997</v>
+        <v>-73.83683583999999</v>
       </c>
       <c r="P61">
-        <v>-151.179488224</v>
+        <v>-156.90327616</v>
       </c>
       <c r="Q61">
-        <v>-64.87948822399996</v>
+        <v>-70.60327615999996</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1204757094984099</v>
+        <v>0.1223426022358702</v>
       </c>
       <c r="T61">
-        <v>0.9732748302544082</v>
+        <v>0.9976067010107683</v>
       </c>
       <c r="U61">
         <v>0.2008</v>
       </c>
       <c r="V61">
-        <v>0.1767458201687539</v>
+        <v>0.1738000564992747</v>
       </c>
       <c r="W61">
-        <v>0.1653094393101142</v>
+        <v>0.1659009486549456</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.552330688027356</v>
+        <v>0.5431251765602334</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1484776100873155</v>
+        <v>0.1500276100873154</v>
       </c>
       <c r="C62">
-        <v>-581.5998022877118</v>
+        <v>-646.669301859818</v>
       </c>
       <c r="D62">
-        <v>1920.040197712288</v>
+        <v>1896.889698140182</v>
       </c>
       <c r="E62">
-        <v>1442.34</v>
+        <v>1484.259</v>
       </c>
       <c r="F62">
-        <v>2515.14</v>
+        <v>2557.059</v>
       </c>
       <c r="G62">
         <v>13.5</v>
@@ -6371,37 +6371,37 @@
         <v>274.3</v>
       </c>
       <c r="M62">
-        <v>505.040112</v>
+        <v>513.4574471999999</v>
       </c>
       <c r="N62">
-        <v>-230.740112</v>
+        <v>-239.1574471999999</v>
       </c>
       <c r="O62">
-        <v>-73.83683583999999</v>
+        <v>-76.53038310399998</v>
       </c>
       <c r="P62">
-        <v>-156.90327616</v>
+        <v>-162.6270640959999</v>
       </c>
       <c r="Q62">
-        <v>-70.60327615999996</v>
+        <v>-76.32706409599994</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1223426022358702</v>
+        <v>0.124305233062431</v>
       </c>
       <c r="T62">
-        <v>0.9976067010107683</v>
+        <v>1.023186360011044</v>
       </c>
       <c r="U62">
         <v>0.2008</v>
       </c>
       <c r="V62">
-        <v>0.1738000564992747</v>
+        <v>0.1709508752451882</v>
       </c>
       <c r="W62">
-        <v>0.1659009486549456</v>
+        <v>0.1664730642507662</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.5431251765602334</v>
+        <v>0.5342214851412131</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1500276100873154</v>
+        <v>0.1515776100873155</v>
       </c>
       <c r="C63">
-        <v>-646.669301859818</v>
+        <v>-711.187187397145</v>
       </c>
       <c r="D63">
-        <v>1896.889698140182</v>
+        <v>1874.290812602855</v>
       </c>
       <c r="E63">
-        <v>1484.259</v>
+        <v>1526.178</v>
       </c>
       <c r="F63">
-        <v>2557.059</v>
+        <v>2598.978</v>
       </c>
       <c r="G63">
         <v>13.5</v>
@@ -6453,37 +6453,37 @@
         <v>274.3</v>
       </c>
       <c r="M63">
-        <v>513.4574471999999</v>
+        <v>521.8747824</v>
       </c>
       <c r="N63">
-        <v>-239.1574471999999</v>
+        <v>-247.5747823999999</v>
       </c>
       <c r="O63">
-        <v>-76.53038310399998</v>
+        <v>-79.22393036799998</v>
       </c>
       <c r="P63">
-        <v>-162.6270640959999</v>
+        <v>-168.350852032</v>
       </c>
       <c r="Q63">
-        <v>-76.32706409599994</v>
+        <v>-82.05085203199998</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.124305233062431</v>
+        <v>0.1263711602482844</v>
       </c>
       <c r="T63">
-        <v>1.023186360011044</v>
+        <v>1.05011231685344</v>
       </c>
       <c r="U63">
         <v>0.2008</v>
       </c>
       <c r="V63">
-        <v>0.1709508752451882</v>
+        <v>0.1681936030638142</v>
       </c>
       <c r="W63">
-        <v>0.1664730642507662</v>
+        <v>0.1670267245047861</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.5342214851412131</v>
+        <v>0.5256050095744194</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1515776100873155</v>
+        <v>0.1531276100873155</v>
       </c>
       <c r="C64">
-        <v>-711.187187397145</v>
+        <v>-775.1729419993139</v>
       </c>
       <c r="D64">
-        <v>1874.290812602855</v>
+        <v>1852.224058000686</v>
       </c>
       <c r="E64">
-        <v>1526.178</v>
+        <v>1568.097</v>
       </c>
       <c r="F64">
-        <v>2598.978</v>
+        <v>2640.897</v>
       </c>
       <c r="G64">
         <v>13.5</v>
@@ -6535,37 +6535,37 @@
         <v>274.3</v>
       </c>
       <c r="M64">
-        <v>521.8747824</v>
+        <v>530.2921176</v>
       </c>
       <c r="N64">
-        <v>-247.5747823999999</v>
+        <v>-255.9921176</v>
       </c>
       <c r="O64">
-        <v>-79.22393036799998</v>
+        <v>-81.91747763199999</v>
       </c>
       <c r="P64">
-        <v>-168.350852032</v>
+        <v>-174.074639968</v>
       </c>
       <c r="Q64">
-        <v>-82.05085203199998</v>
+        <v>-87.77463996799999</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1263711602482844</v>
+        <v>0.1285487591739137</v>
       </c>
       <c r="T64">
-        <v>1.05011231685344</v>
+        <v>1.078493730822452</v>
       </c>
       <c r="U64">
         <v>0.2008</v>
       </c>
       <c r="V64">
-        <v>0.1681936030638142</v>
+        <v>0.1655238633326425</v>
       </c>
       <c r="W64">
-        <v>0.1670267245047861</v>
+        <v>0.1675628082428054</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.5256050095744194</v>
+        <v>0.5172620729145079</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1531276100873155</v>
+        <v>0.1546776100873155</v>
       </c>
       <c r="C65">
-        <v>-775.1729419993139</v>
+        <v>-838.64514191423</v>
       </c>
       <c r="D65">
-        <v>1852.224058000686</v>
+        <v>1830.67085808577</v>
       </c>
       <c r="E65">
-        <v>1568.097</v>
+        <v>1610.016</v>
       </c>
       <c r="F65">
-        <v>2640.897</v>
+        <v>2682.816</v>
       </c>
       <c r="G65">
         <v>13.5</v>
@@ -6617,37 +6617,37 @@
         <v>274.3</v>
       </c>
       <c r="M65">
-        <v>530.2921176</v>
+        <v>538.7094528</v>
       </c>
       <c r="N65">
-        <v>-255.9921176</v>
+        <v>-264.4094528</v>
       </c>
       <c r="O65">
-        <v>-81.91747763199999</v>
+        <v>-84.611024896</v>
       </c>
       <c r="P65">
-        <v>-174.074639968</v>
+        <v>-179.798427904</v>
       </c>
       <c r="Q65">
-        <v>-87.77463996799999</v>
+        <v>-93.498427904</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1285487591739137</v>
+        <v>0.1308473358176336</v>
       </c>
       <c r="T65">
-        <v>1.078493730822452</v>
+        <v>1.108451890011965</v>
       </c>
       <c r="U65">
         <v>0.2008</v>
       </c>
       <c r="V65">
-        <v>0.1655238633326425</v>
+        <v>0.16293755296807</v>
       </c>
       <c r="W65">
-        <v>0.1675628082428054</v>
+        <v>0.1680821393640116</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.5172620729145079</v>
+        <v>0.5091798530252187</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1546776100873155</v>
+        <v>0.1562276100873155</v>
       </c>
       <c r="C66">
-        <v>-838.64514191423</v>
+        <v>-901.6215086935799</v>
       </c>
       <c r="D66">
-        <v>1830.67085808577</v>
+        <v>1809.61349130642</v>
       </c>
       <c r="E66">
-        <v>1610.016</v>
+        <v>1651.935</v>
       </c>
       <c r="F66">
-        <v>2682.816</v>
+        <v>2724.735</v>
       </c>
       <c r="G66">
         <v>13.5</v>
@@ -6699,37 +6699,37 @@
         <v>274.3</v>
       </c>
       <c r="M66">
-        <v>538.7094528</v>
+        <v>547.1267879999999</v>
       </c>
       <c r="N66">
-        <v>-264.4094528</v>
+        <v>-272.8267879999999</v>
       </c>
       <c r="O66">
-        <v>-84.611024896</v>
+        <v>-87.30457215999998</v>
       </c>
       <c r="P66">
-        <v>-179.798427904</v>
+        <v>-185.5222158399999</v>
       </c>
       <c r="Q66">
-        <v>-93.498427904</v>
+        <v>-99.22221583999995</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1308473358176336</v>
+        <v>0.1332772596981374</v>
       </c>
       <c r="T66">
-        <v>1.108451890011965</v>
+        <v>1.140121944012307</v>
       </c>
       <c r="U66">
         <v>0.2008</v>
       </c>
       <c r="V66">
-        <v>0.16293755296807</v>
+        <v>0.1604308213839459</v>
       </c>
       <c r="W66">
-        <v>0.1680821393640116</v>
+        <v>0.1685854910661037</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.5091798530252187</v>
+        <v>0.5013463168248309</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1562276100873155</v>
+        <v>0.1814066840225015</v>
       </c>
       <c r="C67">
-        <v>-901.6215086935799</v>
+        <v>-1228.439205591578</v>
       </c>
       <c r="D67">
-        <v>1809.61349130642</v>
+        <v>1524.714794408422</v>
       </c>
       <c r="E67">
-        <v>1651.935</v>
+        <v>1693.854</v>
       </c>
       <c r="F67">
-        <v>2724.735</v>
+        <v>2766.654</v>
       </c>
       <c r="G67">
         <v>13.5</v>
@@ -6781,45 +6781,45 @@
         <v>274.3</v>
       </c>
       <c r="M67">
-        <v>547.1267879999999</v>
+        <v>652.3770132000001</v>
       </c>
       <c r="N67">
-        <v>-272.8267879999999</v>
+        <v>-378.0770132000001</v>
       </c>
       <c r="O67">
-        <v>-87.30457215999998</v>
+        <v>-120.984644224</v>
       </c>
       <c r="P67">
-        <v>-185.5222158399999</v>
+        <v>-257.092368976</v>
       </c>
       <c r="Q67">
-        <v>-99.22221583999995</v>
+        <v>-170.792368976</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1332772596981374</v>
+        <v>0.1374062200868649</v>
       </c>
       <c r="T67">
-        <v>1.140121944012307</v>
+        <v>1.193936139397374</v>
       </c>
       <c r="U67">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.1604308213839459</v>
+        <v>0.1345479657068947</v>
       </c>
       <c r="W67">
-        <v>0.1685854910661037</v>
+        <v>0.2040735896863143</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y67">
-        <v>0.5013463168248309</v>
+        <v>0.420462392834046</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1814066840225015</v>
+        <v>0.1833066840225015</v>
       </c>
       <c r="C68">
-        <v>-1228.439205591578</v>
+        <v>-1288.259237368272</v>
       </c>
       <c r="D68">
-        <v>1524.714794408422</v>
+        <v>1506.813762631728</v>
       </c>
       <c r="E68">
-        <v>1693.854</v>
+        <v>1735.773</v>
       </c>
       <c r="F68">
-        <v>2766.654</v>
+        <v>2808.573</v>
       </c>
       <c r="G68">
         <v>13.5</v>
@@ -6863,37 +6863,37 @@
         <v>274.3</v>
       </c>
       <c r="M68">
-        <v>652.3770132000001</v>
+        <v>662.2615134</v>
       </c>
       <c r="N68">
-        <v>-378.0770132000001</v>
+        <v>-387.9615134</v>
       </c>
       <c r="O68">
-        <v>-120.984644224</v>
+        <v>-124.147684288</v>
       </c>
       <c r="P68">
-        <v>-257.092368976</v>
+        <v>-263.813829112</v>
       </c>
       <c r="Q68">
-        <v>-170.792368976</v>
+        <v>-177.513829112</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1374062200868649</v>
+        <v>0.1401821661501033</v>
       </c>
       <c r="T68">
-        <v>1.193936139397374</v>
+        <v>1.230116022409416</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.1345479657068947</v>
+        <v>0.1325397871142545</v>
       </c>
       <c r="W68">
-        <v>0.2040735896863143</v>
+        <v>0.2045471181984588</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.420462392834046</v>
+        <v>0.4141868347320453</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1833066840225015</v>
+        <v>0.1852066840225015</v>
       </c>
       <c r="C69">
-        <v>-1288.259237368272</v>
+        <v>-1347.663809983675</v>
       </c>
       <c r="D69">
-        <v>1506.813762631728</v>
+        <v>1489.328190016324</v>
       </c>
       <c r="E69">
-        <v>1735.773</v>
+        <v>1777.692</v>
       </c>
       <c r="F69">
-        <v>2808.573</v>
+        <v>2850.492</v>
       </c>
       <c r="G69">
         <v>13.5</v>
@@ -6945,37 +6945,37 @@
         <v>274.3</v>
       </c>
       <c r="M69">
-        <v>662.2615134</v>
+        <v>672.1460135999999</v>
       </c>
       <c r="N69">
-        <v>-387.9615134</v>
+        <v>-397.8460135999999</v>
       </c>
       <c r="O69">
-        <v>-124.147684288</v>
+        <v>-127.310724352</v>
       </c>
       <c r="P69">
-        <v>-263.813829112</v>
+        <v>-270.535289248</v>
       </c>
       <c r="Q69">
-        <v>-177.513829112</v>
+        <v>-184.235289248</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1401821661501033</v>
+        <v>0.143131608842294</v>
       </c>
       <c r="T69">
-        <v>1.230116022409416</v>
+        <v>1.26855714810971</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.1325397871142545</v>
+        <v>0.1305906725978684</v>
       </c>
       <c r="W69">
-        <v>0.2045471181984588</v>
+        <v>0.2050067194014226</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.4141868347320453</v>
+        <v>0.4080958518683387</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1852066840225015</v>
+        <v>0.1871066840225015</v>
       </c>
       <c r="C70">
-        <v>-1347.663809983675</v>
+        <v>-1406.667220907778</v>
       </c>
       <c r="D70">
-        <v>1489.328190016324</v>
+        <v>1472.243779092222</v>
       </c>
       <c r="E70">
-        <v>1777.692</v>
+        <v>1819.611</v>
       </c>
       <c r="F70">
-        <v>2850.492</v>
+        <v>2892.411</v>
       </c>
       <c r="G70">
         <v>13.5</v>
@@ -7027,37 +7027,37 @@
         <v>274.3</v>
       </c>
       <c r="M70">
-        <v>672.1460135999999</v>
+        <v>682.0305138</v>
       </c>
       <c r="N70">
-        <v>-397.8460135999999</v>
+        <v>-407.7305138</v>
       </c>
       <c r="O70">
-        <v>-127.310724352</v>
+        <v>-130.473764416</v>
       </c>
       <c r="P70">
-        <v>-270.535289248</v>
+        <v>-277.256749384</v>
       </c>
       <c r="Q70">
-        <v>-184.235289248</v>
+        <v>-190.956749384</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.143131608842294</v>
+        <v>0.1462713381597873</v>
       </c>
       <c r="T70">
-        <v>1.26855714810971</v>
+        <v>1.30947834643583</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.1305906725978684</v>
+        <v>0.128698054154421</v>
       </c>
       <c r="W70">
-        <v>0.2050067194014226</v>
+        <v>0.2054529988303875</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.4080958518683387</v>
+        <v>0.4021814192325658</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1871066840225015</v>
+        <v>0.1890066840225015</v>
       </c>
       <c r="C71">
-        <v>-1406.667220907778</v>
+        <v>-1465.283119013093</v>
       </c>
       <c r="D71">
-        <v>1472.243779092222</v>
+        <v>1455.546880986907</v>
       </c>
       <c r="E71">
-        <v>1819.611</v>
+        <v>1861.53</v>
       </c>
       <c r="F71">
-        <v>2892.411</v>
+        <v>2934.33</v>
       </c>
       <c r="G71">
         <v>13.5</v>
@@ -7109,37 +7109,37 @@
         <v>274.3</v>
       </c>
       <c r="M71">
-        <v>682.0305138</v>
+        <v>691.915014</v>
       </c>
       <c r="N71">
-        <v>-407.7305138</v>
+        <v>-417.615014</v>
       </c>
       <c r="O71">
-        <v>-130.473764416</v>
+        <v>-133.63680448</v>
       </c>
       <c r="P71">
-        <v>-277.256749384</v>
+        <v>-283.97820952</v>
       </c>
       <c r="Q71">
-        <v>-190.956749384</v>
+        <v>-197.67820952</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1462713381597873</v>
+        <v>0.1496203827651136</v>
       </c>
       <c r="T71">
-        <v>1.30947834643583</v>
+        <v>1.353127624650358</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.128698054154421</v>
+        <v>0.1268595105236436</v>
       </c>
       <c r="W71">
-        <v>0.2054529988303875</v>
+        <v>0.2058865274185248</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.4021814192325658</v>
+        <v>0.3964359703863862</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1890066840225015</v>
+        <v>0.1909066840225015</v>
       </c>
       <c r="C72">
-        <v>-1465.283119013093</v>
+        <v>-1523.52454094134</v>
       </c>
       <c r="D72">
-        <v>1455.546880986907</v>
+        <v>1439.224459058661</v>
       </c>
       <c r="E72">
-        <v>1861.53</v>
+        <v>1903.449</v>
       </c>
       <c r="F72">
-        <v>2934.33</v>
+        <v>2976.249</v>
       </c>
       <c r="G72">
         <v>13.5</v>
@@ -7191,37 +7191,37 @@
         <v>274.3</v>
       </c>
       <c r="M72">
-        <v>691.915014</v>
+        <v>701.7995142000001</v>
       </c>
       <c r="N72">
-        <v>-417.615014</v>
+        <v>-427.4995142000001</v>
       </c>
       <c r="O72">
-        <v>-133.63680448</v>
+        <v>-136.799844544</v>
       </c>
       <c r="P72">
-        <v>-283.97820952</v>
+        <v>-290.6996696560001</v>
       </c>
       <c r="Q72">
-        <v>-197.67820952</v>
+        <v>-204.3996696560001</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1496203827651136</v>
+        <v>0.1532003959639106</v>
       </c>
       <c r="T72">
-        <v>1.353127624650358</v>
+        <v>1.399787197914163</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.1268595105236436</v>
+        <v>0.1250727568542965</v>
       </c>
       <c r="W72">
-        <v>0.2058865274185248</v>
+        <v>0.2063078439337569</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.3964359703863862</v>
+        <v>0.3908523651696765</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1909066840225015</v>
+        <v>0.1928066840225015</v>
       </c>
       <c r="C73">
-        <v>-1523.524540941339</v>
+        <v>-1581.403945050373</v>
       </c>
       <c r="D73">
-        <v>1439.224459058661</v>
+        <v>1423.264054949627</v>
       </c>
       <c r="E73">
-        <v>1903.449</v>
+        <v>1945.368</v>
       </c>
       <c r="F73">
-        <v>2976.249</v>
+        <v>3018.168</v>
       </c>
       <c r="G73">
         <v>13.5</v>
@@ -7273,37 +7273,37 @@
         <v>274.3</v>
       </c>
       <c r="M73">
-        <v>701.7995142</v>
+        <v>711.6840143999999</v>
       </c>
       <c r="N73">
-        <v>-427.4995142</v>
+        <v>-437.3840143999999</v>
       </c>
       <c r="O73">
-        <v>-136.799844544</v>
+        <v>-139.962884608</v>
       </c>
       <c r="P73">
-        <v>-290.699669656</v>
+        <v>-297.4211297919999</v>
       </c>
       <c r="Q73">
-        <v>-204.399669656</v>
+        <v>-211.1211297919999</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1532003959639106</v>
+        <v>0.1570361243911931</v>
       </c>
       <c r="T73">
-        <v>1.399787197914163</v>
+        <v>1.449779597839669</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.1250727568542965</v>
+        <v>0.1233356352313202</v>
       </c>
       <c r="W73">
-        <v>0.2063078439337569</v>
+        <v>0.2067174572124547</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.3908523651696766</v>
+        <v>0.3854238600978755</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1928066840225015</v>
+        <v>0.1947066840225015</v>
       </c>
       <c r="C74">
-        <v>-1581.403945050373</v>
+        <v>-1638.933243127148</v>
       </c>
       <c r="D74">
-        <v>1423.264054949627</v>
+        <v>1407.653756872852</v>
       </c>
       <c r="E74">
-        <v>1945.368</v>
+        <v>1987.287</v>
       </c>
       <c r="F74">
-        <v>3018.168</v>
+        <v>3060.087</v>
       </c>
       <c r="G74">
         <v>13.5</v>
@@ -7355,37 +7355,37 @@
         <v>274.3</v>
       </c>
       <c r="M74">
-        <v>711.6840143999999</v>
+        <v>721.5685146</v>
       </c>
       <c r="N74">
-        <v>-437.3840143999999</v>
+        <v>-447.2685145999999</v>
       </c>
       <c r="O74">
-        <v>-139.962884608</v>
+        <v>-143.125924672</v>
       </c>
       <c r="P74">
-        <v>-297.4211297919999</v>
+        <v>-304.1425899279999</v>
       </c>
       <c r="Q74">
-        <v>-211.1211297919999</v>
+        <v>-217.8425899279999</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1570361243911931</v>
+        <v>0.1611559808501262</v>
       </c>
       <c r="T74">
-        <v>1.449779597839669</v>
+        <v>1.503475138500397</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.1233356352313202</v>
+        <v>0.121646105981576</v>
       </c>
       <c r="W74">
-        <v>0.2067174572124547</v>
+        <v>0.2071158482095444</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.3854238600978755</v>
+        <v>0.3801440811924252</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1947066840225015</v>
+        <v>0.1966066840225015</v>
       </c>
       <c r="C75">
-        <v>-1638.933243127148</v>
+        <v>-1696.123830036358</v>
       </c>
       <c r="D75">
-        <v>1407.653756872852</v>
+        <v>1392.382169963641</v>
       </c>
       <c r="E75">
-        <v>1987.287</v>
+        <v>2029.206</v>
       </c>
       <c r="F75">
-        <v>3060.087</v>
+        <v>3102.006</v>
       </c>
       <c r="G75">
         <v>13.5</v>
@@ -7437,37 +7437,37 @@
         <v>274.3</v>
       </c>
       <c r="M75">
-        <v>721.5685146</v>
+        <v>731.4530148</v>
       </c>
       <c r="N75">
-        <v>-447.2685145999999</v>
+        <v>-457.1530148</v>
       </c>
       <c r="O75">
-        <v>-143.125924672</v>
+        <v>-146.288964736</v>
       </c>
       <c r="P75">
-        <v>-304.1425899279999</v>
+        <v>-310.864050064</v>
       </c>
       <c r="Q75">
-        <v>-217.8425899279999</v>
+        <v>-224.564050064</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1611559808501262</v>
+        <v>0.1655927493443618</v>
       </c>
       <c r="T75">
-        <v>1.503475138500397</v>
+        <v>1.561301105365797</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.121646105981576</v>
+        <v>0.1200022396845277</v>
       </c>
       <c r="W75">
-        <v>0.2071158482095444</v>
+        <v>0.2075034718823884</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.3801440811924252</v>
+        <v>0.3750069990141491</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1966066840225015</v>
+        <v>0.1985066840225015</v>
       </c>
       <c r="C76">
-        <v>-1696.123830036358</v>
+        <v>-1752.986611459856</v>
       </c>
       <c r="D76">
-        <v>1392.382169963641</v>
+        <v>1377.438388540143</v>
       </c>
       <c r="E76">
-        <v>2029.206</v>
+        <v>2071.125</v>
       </c>
       <c r="F76">
-        <v>3102.006</v>
+        <v>3143.925</v>
       </c>
       <c r="G76">
         <v>13.5</v>
@@ -7519,37 +7519,37 @@
         <v>274.3</v>
       </c>
       <c r="M76">
-        <v>731.4530148</v>
+        <v>741.3375149999999</v>
       </c>
       <c r="N76">
-        <v>-457.1530148</v>
+        <v>-467.0375149999999</v>
       </c>
       <c r="O76">
-        <v>-146.288964736</v>
+        <v>-149.4520048</v>
       </c>
       <c r="P76">
-        <v>-310.864050064</v>
+        <v>-317.5855101999999</v>
       </c>
       <c r="Q76">
-        <v>-224.564050064</v>
+        <v>-231.2855101999999</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1655927493443618</v>
+        <v>0.1703844593181363</v>
       </c>
       <c r="T76">
-        <v>1.561301105365797</v>
+        <v>1.623753149580429</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.1200022396845277</v>
+        <v>0.1184022098220674</v>
       </c>
       <c r="W76">
-        <v>0.2075034718823884</v>
+        <v>0.2078807589239565</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.3750069990141491</v>
+        <v>0.3700069056939606</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1985066840225015</v>
+        <v>0.2004066840225014</v>
       </c>
       <c r="C77">
-        <v>-1752.986611459856</v>
+        <v>-1809.532029868747</v>
       </c>
       <c r="D77">
-        <v>1377.438388540143</v>
+        <v>1362.811970131252</v>
       </c>
       <c r="E77">
-        <v>2071.125</v>
+        <v>2113.044</v>
       </c>
       <c r="F77">
-        <v>3143.925</v>
+        <v>3185.844</v>
       </c>
       <c r="G77">
         <v>13.5</v>
@@ -7601,37 +7601,37 @@
         <v>274.3</v>
       </c>
       <c r="M77">
-        <v>741.3375149999999</v>
+        <v>751.2220152</v>
       </c>
       <c r="N77">
-        <v>-467.0375149999999</v>
+        <v>-476.9220152</v>
       </c>
       <c r="O77">
-        <v>-149.4520048</v>
+        <v>-152.615044864</v>
       </c>
       <c r="P77">
-        <v>-317.5855101999999</v>
+        <v>-324.3069703359999</v>
       </c>
       <c r="Q77">
-        <v>-231.2855101999999</v>
+        <v>-238.0069703359999</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1703844593181363</v>
+        <v>0.175575478456392</v>
       </c>
       <c r="T77">
-        <v>1.623753149580429</v>
+        <v>1.691409530812947</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.1184022098220674</v>
+        <v>0.1168442860086191</v>
       </c>
       <c r="W77">
-        <v>0.2078807589239565</v>
+        <v>0.2082481173591676</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.3700069056939606</v>
+        <v>0.3651383937769347</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2004066840225014</v>
+        <v>0.2023066840225015</v>
       </c>
       <c r="C78">
-        <v>-1809.532029868747</v>
+        <v>-1865.770088858158</v>
       </c>
       <c r="D78">
-        <v>1362.811970131252</v>
+        <v>1348.492911141842</v>
       </c>
       <c r="E78">
-        <v>2113.044</v>
+        <v>2154.963</v>
       </c>
       <c r="F78">
-        <v>3185.844</v>
+        <v>3227.763</v>
       </c>
       <c r="G78">
         <v>13.5</v>
@@ -7683,37 +7683,37 @@
         <v>274.3</v>
       </c>
       <c r="M78">
-        <v>751.2220152</v>
+        <v>761.1065154</v>
       </c>
       <c r="N78">
-        <v>-476.9220152</v>
+        <v>-486.8065154</v>
       </c>
       <c r="O78">
-        <v>-152.615044864</v>
+        <v>-155.778084928</v>
       </c>
       <c r="P78">
-        <v>-324.3069703359999</v>
+        <v>-331.028430472</v>
       </c>
       <c r="Q78">
-        <v>-238.0069703359999</v>
+        <v>-244.728430472</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.175575478456392</v>
+        <v>0.1812178905631916</v>
       </c>
       <c r="T78">
-        <v>1.691409530812947</v>
+        <v>1.764949075630901</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.1168442860086191</v>
+        <v>0.1153268277487669</v>
       </c>
       <c r="W78">
-        <v>0.2082481173591676</v>
+        <v>0.2086059340168408</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.3651383937769347</v>
+        <v>0.3603963367148966</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2023066840225015</v>
+        <v>0.2042066840225015</v>
       </c>
       <c r="C79">
-        <v>-1865.770088858158</v>
+        <v>-1921.710375963838</v>
       </c>
       <c r="D79">
-        <v>1348.492911141842</v>
+        <v>1334.471624036162</v>
       </c>
       <c r="E79">
-        <v>2154.963</v>
+        <v>2196.882</v>
       </c>
       <c r="F79">
-        <v>3227.763</v>
+        <v>3269.682</v>
       </c>
       <c r="G79">
         <v>13.5</v>
@@ -7765,37 +7765,37 @@
         <v>274.3</v>
       </c>
       <c r="M79">
-        <v>761.1065154</v>
+        <v>770.9910156</v>
       </c>
       <c r="N79">
-        <v>-486.8065154</v>
+        <v>-496.6910156</v>
       </c>
       <c r="O79">
-        <v>-155.778084928</v>
+        <v>-158.941124992</v>
       </c>
       <c r="P79">
-        <v>-331.028430472</v>
+        <v>-337.749890608</v>
       </c>
       <c r="Q79">
-        <v>-244.728430472</v>
+        <v>-251.449890608</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1812178905631916</v>
+        <v>0.1873732492251549</v>
       </c>
       <c r="T79">
-        <v>1.764949075630901</v>
+        <v>1.845174033614124</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.1153268277487669</v>
+        <v>0.1138482786750648</v>
       </c>
       <c r="W79">
-        <v>0.2086059340168408</v>
+        <v>0.2089545758884197</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.3603963367148966</v>
+        <v>0.3557758708595774</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2042066840225015</v>
+        <v>0.2061066840225015</v>
       </c>
       <c r="C80">
-        <v>-1921.710375963838</v>
+        <v>-1977.36208406997</v>
       </c>
       <c r="D80">
-        <v>1334.471624036162</v>
+        <v>1320.738915930029</v>
       </c>
       <c r="E80">
-        <v>2196.882</v>
+        <v>2238.800999999999</v>
       </c>
       <c r="F80">
-        <v>3269.682</v>
+        <v>3311.601</v>
       </c>
       <c r="G80">
         <v>13.5</v>
@@ -7847,37 +7847,37 @@
         <v>274.3</v>
       </c>
       <c r="M80">
-        <v>770.9910156</v>
+        <v>780.8755157999999</v>
       </c>
       <c r="N80">
-        <v>-496.6910156</v>
+        <v>-506.5755157999999</v>
       </c>
       <c r="O80">
-        <v>-158.941124992</v>
+        <v>-162.104165056</v>
       </c>
       <c r="P80">
-        <v>-337.749890608</v>
+        <v>-344.4713507439999</v>
       </c>
       <c r="Q80">
-        <v>-251.449890608</v>
+        <v>-258.1713507439999</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.1873732492251549</v>
+        <v>0.1941148325215908</v>
       </c>
       <c r="T80">
-        <v>1.845174033614124</v>
+        <v>1.933039463786225</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.1138482786750648</v>
+        <v>0.1124071612234817</v>
       </c>
       <c r="W80">
-        <v>0.2089545758884197</v>
+        <v>0.209294391383503</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.3557758708595774</v>
+        <v>0.3512723788233802</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2061066840225015</v>
+        <v>0.2080066840225015</v>
       </c>
       <c r="C81">
-        <v>-1977.36208406997</v>
+        <v>-2032.734031508626</v>
       </c>
       <c r="D81">
-        <v>1320.738915930029</v>
+        <v>1307.285968491374</v>
       </c>
       <c r="E81">
-        <v>2238.800999999999</v>
+        <v>2280.72</v>
       </c>
       <c r="F81">
-        <v>3311.601</v>
+        <v>3353.52</v>
       </c>
       <c r="G81">
         <v>13.5</v>
@@ -7929,37 +7929,37 @@
         <v>274.3</v>
       </c>
       <c r="M81">
-        <v>780.8755157999999</v>
+        <v>790.7600160000001</v>
       </c>
       <c r="N81">
-        <v>-506.5755157999999</v>
+        <v>-516.460016</v>
       </c>
       <c r="O81">
-        <v>-162.104165056</v>
+        <v>-165.26720512</v>
       </c>
       <c r="P81">
-        <v>-344.4713507439999</v>
+        <v>-351.19281088</v>
       </c>
       <c r="Q81">
-        <v>-258.1713507439999</v>
+        <v>-264.89281088</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.1941148325215908</v>
+        <v>0.2015305741476704</v>
       </c>
       <c r="T81">
-        <v>1.933039463786225</v>
+        <v>2.029691436975537</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.1124071612234817</v>
+        <v>0.1110020717081881</v>
       </c>
       <c r="W81">
-        <v>0.209294391383503</v>
+        <v>0.2096257114912093</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.3512723788233802</v>
+        <v>0.346881474088088</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2080066840225015</v>
+        <v>0.2099066840225015</v>
       </c>
       <c r="C82">
-        <v>-2032.734031508626</v>
+        <v>-2087.834680943213</v>
       </c>
       <c r="D82">
-        <v>1307.285968491374</v>
+        <v>1294.104319056787</v>
       </c>
       <c r="E82">
-        <v>2280.72</v>
+        <v>2322.639</v>
       </c>
       <c r="F82">
-        <v>3353.52</v>
+        <v>3395.439</v>
       </c>
       <c r="G82">
         <v>13.5</v>
@@ -8011,37 +8011,37 @@
         <v>274.3</v>
       </c>
       <c r="M82">
-        <v>790.7600160000001</v>
+        <v>800.6445162</v>
       </c>
       <c r="N82">
-        <v>-516.460016</v>
+        <v>-526.3445162</v>
       </c>
       <c r="O82">
-        <v>-165.26720512</v>
+        <v>-168.430245184</v>
       </c>
       <c r="P82">
-        <v>-351.19281088</v>
+        <v>-357.914271016</v>
       </c>
       <c r="Q82">
-        <v>-264.89281088</v>
+        <v>-271.614271016</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2015305741476704</v>
+        <v>0.2097269201554425</v>
       </c>
       <c r="T82">
-        <v>2.029691436975537</v>
+        <v>2.136517302079512</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.1110020717081881</v>
+        <v>0.1096316757611735</v>
       </c>
       <c r="W82">
-        <v>0.2096257114912093</v>
+        <v>0.2099488508555153</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.346881474088088</v>
+        <v>0.3425989867536671</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2099066840225015</v>
+        <v>0.2118066840225015</v>
       </c>
       <c r="C83">
-        <v>-2087.834680943213</v>
+        <v>-2142.672157120907</v>
       </c>
       <c r="D83">
-        <v>1294.104319056787</v>
+        <v>1281.185842879093</v>
       </c>
       <c r="E83">
-        <v>2322.639</v>
+        <v>2364.558</v>
       </c>
       <c r="F83">
-        <v>3395.439</v>
+        <v>3437.358</v>
       </c>
       <c r="G83">
         <v>13.5</v>
@@ -8093,37 +8093,37 @@
         <v>274.3</v>
       </c>
       <c r="M83">
-        <v>800.6445162</v>
+        <v>810.5290164</v>
       </c>
       <c r="N83">
-        <v>-526.3445162</v>
+        <v>-536.2290164000001</v>
       </c>
       <c r="O83">
-        <v>-168.430245184</v>
+        <v>-171.593285248</v>
       </c>
       <c r="P83">
-        <v>-357.914271016</v>
+        <v>-364.6357311520001</v>
       </c>
       <c r="Q83">
-        <v>-271.614271016</v>
+        <v>-278.3357311520001</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2097269201554425</v>
+        <v>0.2188339712751894</v>
       </c>
       <c r="T83">
-        <v>2.136517302079512</v>
+        <v>2.255212707750597</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.1096316757611735</v>
+        <v>0.1082947041055494</v>
       </c>
       <c r="W83">
-        <v>0.2099488508555153</v>
+        <v>0.2102641087719115</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.3425989867536671</v>
+        <v>0.3384209503298418</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2118066840225015</v>
+        <v>0.2137066840225015</v>
       </c>
       <c r="C84">
-        <v>-2142.672157120907</v>
+        <v>-2197.254263572285</v>
       </c>
       <c r="D84">
-        <v>1281.185842879093</v>
+        <v>1268.522736427715</v>
       </c>
       <c r="E84">
-        <v>2364.558</v>
+        <v>2406.477</v>
       </c>
       <c r="F84">
-        <v>3437.358</v>
+        <v>3479.277</v>
       </c>
       <c r="G84">
         <v>13.5</v>
@@ -8175,37 +8175,37 @@
         <v>274.3</v>
       </c>
       <c r="M84">
-        <v>810.5290164</v>
+        <v>820.4135166000001</v>
       </c>
       <c r="N84">
-        <v>-536.2290164000001</v>
+        <v>-546.1135166000001</v>
       </c>
       <c r="O84">
-        <v>-171.593285248</v>
+        <v>-174.7563253120001</v>
       </c>
       <c r="P84">
-        <v>-364.6357311520001</v>
+        <v>-371.3571912880001</v>
       </c>
       <c r="Q84">
-        <v>-278.3357311520001</v>
+        <v>-285.0571912880001</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2188339712751894</v>
+        <v>0.2290124401737299</v>
       </c>
       <c r="T84">
-        <v>2.255212707750597</v>
+        <v>2.38787227879475</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.1082947041055494</v>
+        <v>0.1069899486343982</v>
       </c>
       <c r="W84">
-        <v>0.2102641087719115</v>
+        <v>0.2105717701120089</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.3384209503298418</v>
+        <v>0.3343435894824943</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2137066840225015</v>
+        <v>0.2156066840225015</v>
       </c>
       <c r="C85">
-        <v>-2197.254263572285</v>
+        <v>-2251.588498330322</v>
       </c>
       <c r="D85">
-        <v>1268.522736427715</v>
+        <v>1256.107501669678</v>
       </c>
       <c r="E85">
-        <v>2406.477</v>
+        <v>2448.396</v>
       </c>
       <c r="F85">
-        <v>3479.277</v>
+        <v>3521.196</v>
       </c>
       <c r="G85">
         <v>13.5</v>
@@ -8257,37 +8257,37 @@
         <v>274.3</v>
       </c>
       <c r="M85">
-        <v>820.4135166000001</v>
+        <v>830.2980168</v>
       </c>
       <c r="N85">
-        <v>-546.1135166000001</v>
+        <v>-555.9980168</v>
       </c>
       <c r="O85">
-        <v>-174.7563253120001</v>
+        <v>-177.919365376</v>
       </c>
       <c r="P85">
-        <v>-371.3571912880001</v>
+        <v>-378.078651424</v>
       </c>
       <c r="Q85">
-        <v>-285.0571912880001</v>
+        <v>-291.778651424</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2290124401737299</v>
+        <v>0.2404632176845881</v>
       </c>
       <c r="T85">
-        <v>2.38787227879475</v>
+        <v>2.537114296219422</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.1069899486343982</v>
+        <v>0.105716258769703</v>
       </c>
       <c r="W85">
-        <v>0.2105717701120089</v>
+        <v>0.210872106182104</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.3343435894824943</v>
+        <v>0.3303633086553219</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2156066840225014</v>
+        <v>0.2175066840225015</v>
       </c>
       <c r="C86">
-        <v>-2251.588498330321</v>
+        <v>-2305.682068735261</v>
       </c>
       <c r="D86">
-        <v>1256.107501669678</v>
+        <v>1243.932931264739</v>
       </c>
       <c r="E86">
-        <v>2448.396</v>
+        <v>2490.315</v>
       </c>
       <c r="F86">
-        <v>3521.195999999999</v>
+        <v>3563.115</v>
       </c>
       <c r="G86">
         <v>13.5</v>
@@ -8339,37 +8339,37 @@
         <v>274.3</v>
       </c>
       <c r="M86">
-        <v>830.2980167999999</v>
+        <v>840.182517</v>
       </c>
       <c r="N86">
-        <v>-555.9980168</v>
+        <v>-565.882517</v>
       </c>
       <c r="O86">
-        <v>-177.919365376</v>
+        <v>-181.08240544</v>
       </c>
       <c r="P86">
-        <v>-378.078651424</v>
+        <v>-384.80011156</v>
       </c>
       <c r="Q86">
-        <v>-291.778651424</v>
+        <v>-298.50011156</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2404632176845879</v>
+        <v>0.2534407655302271</v>
       </c>
       <c r="T86">
-        <v>2.53711429621942</v>
+        <v>2.706255249300715</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.105716258769703</v>
+        <v>0.1044725380782947</v>
       </c>
       <c r="W86">
-        <v>0.210872106182104</v>
+        <v>0.2111653755211381</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.3303633086553218</v>
+        <v>0.3264766814946709</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2175066840225015</v>
+        <v>0.2194066840225015</v>
       </c>
       <c r="C87">
-        <v>-2305.682068735261</v>
+        <v>-2359.541905386789</v>
       </c>
       <c r="D87">
-        <v>1243.932931264739</v>
+        <v>1231.992094613211</v>
       </c>
       <c r="E87">
-        <v>2490.315</v>
+        <v>2532.233999999999</v>
       </c>
       <c r="F87">
-        <v>3563.115</v>
+        <v>3605.034</v>
       </c>
       <c r="G87">
         <v>13.5</v>
@@ -8421,37 +8421,37 @@
         <v>274.3</v>
       </c>
       <c r="M87">
-        <v>840.182517</v>
+        <v>850.0670171999999</v>
       </c>
       <c r="N87">
-        <v>-565.882517</v>
+        <v>-575.7670171999998</v>
       </c>
       <c r="O87">
-        <v>-181.08240544</v>
+        <v>-184.2454455039999</v>
       </c>
       <c r="P87">
-        <v>-384.80011156</v>
+        <v>-391.5215716959999</v>
       </c>
       <c r="Q87">
-        <v>-298.50011156</v>
+        <v>-305.2215716959999</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2534407655302271</v>
+        <v>0.2682722487823862</v>
       </c>
       <c r="T87">
-        <v>2.706255249300715</v>
+        <v>2.899559195679337</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.1044725380782947</v>
+        <v>0.103257741123896</v>
       </c>
       <c r="W87">
-        <v>0.2111653755211381</v>
+        <v>0.2114518246429853</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.3264766814946709</v>
+        <v>0.322680441012175</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2194066840225015</v>
+        <v>0.2213066840225015</v>
       </c>
       <c r="C88">
-        <v>-2359.541905386789</v>
+        <v>-2413.174675300272</v>
       </c>
       <c r="D88">
-        <v>1231.992094613211</v>
+        <v>1220.278324699728</v>
       </c>
       <c r="E88">
-        <v>2532.233999999999</v>
+        <v>2574.152999999999</v>
       </c>
       <c r="F88">
-        <v>3605.034</v>
+        <v>3646.953</v>
       </c>
       <c r="G88">
         <v>13.5</v>
@@ -8503,37 +8503,37 @@
         <v>274.3</v>
       </c>
       <c r="M88">
-        <v>850.0670171999999</v>
+        <v>859.9515173999999</v>
       </c>
       <c r="N88">
-        <v>-575.7670171999998</v>
+        <v>-585.6515173999999</v>
       </c>
       <c r="O88">
-        <v>-184.2454455039999</v>
+        <v>-187.408485568</v>
       </c>
       <c r="P88">
-        <v>-391.5215716959999</v>
+        <v>-398.2430318319999</v>
       </c>
       <c r="Q88">
-        <v>-305.2215716959999</v>
+        <v>-311.9430318319999</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.2682722487823862</v>
+        <v>0.2853854986887236</v>
       </c>
       <c r="T88">
-        <v>2.899559195679337</v>
+        <v>3.122602210731594</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.103257741123896</v>
+        <v>0.102070870536265</v>
       </c>
       <c r="W88">
-        <v>0.2114518246429853</v>
+        <v>0.2117316887275487</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.322680441012175</v>
+        <v>0.3189714704258281</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2213066840225015</v>
+        <v>0.2232066840225015</v>
       </c>
       <c r="C89">
-        <v>-2413.174675300272</v>
+        <v>-2466.586794319521</v>
       </c>
       <c r="D89">
-        <v>1220.278324699728</v>
+        <v>1208.785205680479</v>
       </c>
       <c r="E89">
-        <v>2574.152999999999</v>
+        <v>2616.072</v>
       </c>
       <c r="F89">
-        <v>3646.953</v>
+        <v>3688.872</v>
       </c>
       <c r="G89">
         <v>13.5</v>
@@ -8585,37 +8585,37 @@
         <v>274.3</v>
       </c>
       <c r="M89">
-        <v>859.9515173999999</v>
+        <v>869.8360176</v>
       </c>
       <c r="N89">
-        <v>-585.6515173999999</v>
+        <v>-595.5360175999999</v>
       </c>
       <c r="O89">
-        <v>-187.408485568</v>
+        <v>-190.571525632</v>
       </c>
       <c r="P89">
-        <v>-398.2430318319999</v>
+        <v>-404.9644919679999</v>
       </c>
       <c r="Q89">
-        <v>-311.9430318319999</v>
+        <v>-318.6644919679999</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.2853854986887236</v>
+        <v>0.3053509569127839</v>
       </c>
       <c r="T89">
-        <v>3.122602210731594</v>
+        <v>3.382819061625894</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.102070870536265</v>
+        <v>0.100910974280171</v>
       </c>
       <c r="W89">
-        <v>0.2117316887275487</v>
+        <v>0.2120051922647357</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.3189714704258281</v>
+        <v>0.3153467946255346</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2232066840225015</v>
+        <v>0.2251066840225015</v>
       </c>
       <c r="C90">
-        <v>-2466.586794319521</v>
+        <v>-2519.784438834649</v>
       </c>
       <c r="D90">
-        <v>1208.785205680479</v>
+        <v>1197.50656116535</v>
       </c>
       <c r="E90">
-        <v>2616.072</v>
+        <v>2657.991</v>
       </c>
       <c r="F90">
-        <v>3688.872</v>
+        <v>3730.791</v>
       </c>
       <c r="G90">
         <v>13.5</v>
@@ -8667,37 +8667,37 @@
         <v>274.3</v>
       </c>
       <c r="M90">
-        <v>869.8360176</v>
+        <v>879.7205177999999</v>
       </c>
       <c r="N90">
-        <v>-595.5360175999999</v>
+        <v>-605.4205178</v>
       </c>
       <c r="O90">
-        <v>-190.571525632</v>
+        <v>-193.734565696</v>
       </c>
       <c r="P90">
-        <v>-404.9644919679999</v>
+        <v>-411.685952104</v>
       </c>
       <c r="Q90">
-        <v>-318.6644919679999</v>
+        <v>-325.385952104</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3053509569127839</v>
+        <v>0.3289464984503098</v>
       </c>
       <c r="T90">
-        <v>3.382819061625894</v>
+        <v>3.690348067228248</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.100910974280171</v>
+        <v>0.09977714310848373</v>
       </c>
       <c r="W90">
-        <v>0.2120051922647357</v>
+        <v>0.2122725496550195</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.3153467946255346</v>
+        <v>0.3118035722140116</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2251066840225015</v>
+        <v>0.2270066840225015</v>
       </c>
       <c r="C91">
-        <v>-2519.784438834649</v>
+        <v>-2572.773556849992</v>
       </c>
       <c r="D91">
-        <v>1197.50656116535</v>
+        <v>1186.436443150008</v>
       </c>
       <c r="E91">
-        <v>2657.991</v>
+        <v>2699.91</v>
       </c>
       <c r="F91">
-        <v>3730.791</v>
+        <v>3772.71</v>
       </c>
       <c r="G91">
         <v>13.5</v>
@@ -8749,37 +8749,37 @@
         <v>274.3</v>
       </c>
       <c r="M91">
-        <v>879.7205177999999</v>
+        <v>889.605018</v>
       </c>
       <c r="N91">
-        <v>-605.4205178</v>
+        <v>-615.305018</v>
       </c>
       <c r="O91">
-        <v>-193.734565696</v>
+        <v>-196.89760576</v>
       </c>
       <c r="P91">
-        <v>-411.685952104</v>
+        <v>-418.40741224</v>
       </c>
       <c r="Q91">
-        <v>-325.385952104</v>
+        <v>-332.10741224</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.3289464984503098</v>
+        <v>0.3572611482953408</v>
       </c>
       <c r="T91">
-        <v>3.690348067228248</v>
+        <v>4.059382873951074</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.09977714310848373</v>
+        <v>0.09866850818505613</v>
       </c>
       <c r="W91">
-        <v>0.2122725496550195</v>
+        <v>0.2125339657699638</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.3118035722140116</v>
+        <v>0.3083390880783003</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2270066840225015</v>
+        <v>0.2289066840225015</v>
       </c>
       <c r="C92">
-        <v>-2572.773556849992</v>
+        <v>-2625.559878443751</v>
       </c>
       <c r="D92">
-        <v>1186.436443150008</v>
+        <v>1175.569121556249</v>
       </c>
       <c r="E92">
-        <v>2699.91</v>
+        <v>2741.829</v>
       </c>
       <c r="F92">
-        <v>3772.71</v>
+        <v>3814.629</v>
       </c>
       <c r="G92">
         <v>13.5</v>
@@ -8831,37 +8831,37 @@
         <v>274.3</v>
       </c>
       <c r="M92">
-        <v>889.605018</v>
+        <v>899.4895182</v>
       </c>
       <c r="N92">
-        <v>-615.305018</v>
+        <v>-625.1895182000001</v>
       </c>
       <c r="O92">
-        <v>-196.89760576</v>
+        <v>-200.060645824</v>
       </c>
       <c r="P92">
-        <v>-418.40741224</v>
+        <v>-425.128872376</v>
       </c>
       <c r="Q92">
-        <v>-332.10741224</v>
+        <v>-338.828872376</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.3572611482953408</v>
+        <v>0.3918679425503787</v>
       </c>
       <c r="T92">
-        <v>4.059382873951074</v>
+        <v>4.510425415501193</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.09866850818505613</v>
+        <v>0.09758423886434123</v>
       </c>
       <c r="W92">
-        <v>0.2125339657699638</v>
+        <v>0.2127896364757884</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.3083390880783003</v>
+        <v>0.3049507464510662</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2289066840225015</v>
+        <v>0.2308066840225015</v>
       </c>
       <c r="C93">
-        <v>-2625.559878443751</v>
+        <v>-2678.148925658025</v>
       </c>
       <c r="D93">
-        <v>1175.569121556249</v>
+        <v>1164.899074341975</v>
       </c>
       <c r="E93">
-        <v>2741.829</v>
+        <v>2783.748</v>
       </c>
       <c r="F93">
-        <v>3814.629</v>
+        <v>3856.548</v>
       </c>
       <c r="G93">
         <v>13.5</v>
@@ -8913,37 +8913,37 @@
         <v>274.3</v>
       </c>
       <c r="M93">
-        <v>899.4895182</v>
+        <v>909.3740184</v>
       </c>
       <c r="N93">
-        <v>-625.1895182000001</v>
+        <v>-635.0740183999999</v>
       </c>
       <c r="O93">
-        <v>-200.060645824</v>
+        <v>-203.223685888</v>
       </c>
       <c r="P93">
-        <v>-425.128872376</v>
+        <v>-431.8503325119999</v>
       </c>
       <c r="Q93">
-        <v>-338.828872376</v>
+        <v>-345.5503325119999</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.3918679425503787</v>
+        <v>0.4351264353691761</v>
       </c>
       <c r="T93">
-        <v>4.510425415501193</v>
+        <v>5.074228592438843</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.09758423886434123</v>
+        <v>0.09652354061581578</v>
       </c>
       <c r="W93">
-        <v>0.2127896364757884</v>
+        <v>0.2130397491227906</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.3049507464510662</v>
+        <v>0.3016360644244244</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2308066840225015</v>
+        <v>0.2327066840225015</v>
       </c>
       <c r="C94">
-        <v>-2678.148925658025</v>
+        <v>-2730.546021855081</v>
       </c>
       <c r="D94">
-        <v>1164.899074341975</v>
+        <v>1154.420978144919</v>
       </c>
       <c r="E94">
-        <v>2783.748</v>
+        <v>2825.666999999999</v>
       </c>
       <c r="F94">
-        <v>3856.548</v>
+        <v>3898.467</v>
       </c>
       <c r="G94">
         <v>13.5</v>
@@ -8995,37 +8995,37 @@
         <v>274.3</v>
       </c>
       <c r="M94">
-        <v>909.3740184</v>
+        <v>919.2585186</v>
       </c>
       <c r="N94">
-        <v>-635.0740183999999</v>
+        <v>-644.9585185999999</v>
       </c>
       <c r="O94">
-        <v>-203.223685888</v>
+        <v>-206.386725952</v>
       </c>
       <c r="P94">
-        <v>-431.8503325119999</v>
+        <v>-438.5717926479999</v>
       </c>
       <c r="Q94">
-        <v>-345.5503325119999</v>
+        <v>-352.2717926479999</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.4351264353691761</v>
+        <v>0.4907444975647727</v>
       </c>
       <c r="T94">
-        <v>5.074228592438843</v>
+        <v>5.799118391358678</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.09652354061581578</v>
+        <v>0.09548565308231238</v>
       </c>
       <c r="W94">
-        <v>0.2130397491227906</v>
+        <v>0.2132844830031908</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.3016360644244244</v>
+        <v>0.2983926658822262</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2327066840225015</v>
+        <v>0.2346066840225015</v>
       </c>
       <c r="C95">
-        <v>-2730.546021855081</v>
+        <v>-2782.756300573174</v>
       </c>
       <c r="D95">
-        <v>1154.420978144919</v>
+        <v>1144.129699426825</v>
       </c>
       <c r="E95">
-        <v>2825.666999999999</v>
+        <v>2867.586</v>
       </c>
       <c r="F95">
-        <v>3898.467</v>
+        <v>3940.386</v>
       </c>
       <c r="G95">
         <v>13.5</v>
@@ -9077,37 +9077,37 @@
         <v>274.3</v>
       </c>
       <c r="M95">
-        <v>919.2585186</v>
+        <v>929.1430188</v>
       </c>
       <c r="N95">
-        <v>-644.9585185999999</v>
+        <v>-654.8430188</v>
       </c>
       <c r="O95">
-        <v>-206.386725952</v>
+        <v>-209.549766016</v>
       </c>
       <c r="P95">
-        <v>-438.5717926479999</v>
+        <v>-445.2932527839999</v>
       </c>
       <c r="Q95">
-        <v>-352.2717926479999</v>
+        <v>-358.9932527839999</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.4907444975647727</v>
+        <v>0.5649019138255683</v>
       </c>
       <c r="T95">
-        <v>5.799118391358678</v>
+        <v>6.765638123251794</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.09548565308231238</v>
+        <v>0.09446984826228778</v>
       </c>
       <c r="W95">
-        <v>0.2132844830031908</v>
+        <v>0.2135240097797526</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.2983926658822262</v>
+        <v>0.2952182758196493</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2346066840225015</v>
+        <v>0.2365066840225015</v>
       </c>
       <c r="C96">
-        <v>-2782.756300573174</v>
+        <v>-2834.784713912881</v>
       </c>
       <c r="D96">
-        <v>1144.129699426825</v>
+        <v>1134.020286087119</v>
       </c>
       <c r="E96">
-        <v>2867.586</v>
+        <v>2909.505</v>
       </c>
       <c r="F96">
-        <v>3940.386</v>
+        <v>3982.305</v>
       </c>
       <c r="G96">
         <v>13.5</v>
@@ -9159,37 +9159,37 @@
         <v>274.3</v>
       </c>
       <c r="M96">
-        <v>929.1430188</v>
+        <v>939.027519</v>
       </c>
       <c r="N96">
-        <v>-654.8430188</v>
+        <v>-664.727519</v>
       </c>
       <c r="O96">
-        <v>-209.549766016</v>
+        <v>-212.71280608</v>
       </c>
       <c r="P96">
-        <v>-445.2932527839999</v>
+        <v>-452.01471292</v>
       </c>
       <c r="Q96">
-        <v>-358.9932527839999</v>
+        <v>-365.71471292</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.5649019138255683</v>
+        <v>0.6687222965906822</v>
       </c>
       <c r="T96">
-        <v>6.765638123251794</v>
+        <v>8.118765747902156</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.09446984826228778</v>
+        <v>0.09347542880689527</v>
       </c>
       <c r="W96">
-        <v>0.2135240097797526</v>
+        <v>0.2137584938873341</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.2952182758196493</v>
+        <v>0.2921107150215477</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2365066840225015</v>
+        <v>0.2384066840225015</v>
       </c>
       <c r="C97">
-        <v>-2834.784713912881</v>
+        <v>-2886.63604048271</v>
       </c>
       <c r="D97">
-        <v>1134.020286087119</v>
+        <v>1124.08795951729</v>
       </c>
       <c r="E97">
-        <v>2909.505</v>
+        <v>2951.424</v>
       </c>
       <c r="F97">
-        <v>3982.305</v>
+        <v>4024.224</v>
       </c>
       <c r="G97">
         <v>13.5</v>
@@ -9241,37 +9241,37 @@
         <v>274.3</v>
       </c>
       <c r="M97">
-        <v>939.027519</v>
+        <v>948.9120192</v>
       </c>
       <c r="N97">
-        <v>-664.727519</v>
+        <v>-674.6120192000001</v>
       </c>
       <c r="O97">
-        <v>-212.71280608</v>
+        <v>-215.875846144</v>
       </c>
       <c r="P97">
-        <v>-452.01471292</v>
+        <v>-458.736173056</v>
       </c>
       <c r="Q97">
-        <v>-365.71471292</v>
+        <v>-372.436173056</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.6687222965906822</v>
+        <v>0.8244528707383533</v>
       </c>
       <c r="T97">
-        <v>8.118765747902156</v>
+        <v>10.1484571848777</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.09347542880689527</v>
+        <v>0.09250172642349012</v>
       </c>
       <c r="W97">
-        <v>0.2137584938873341</v>
+        <v>0.213988092909341</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.2921107150215477</v>
+        <v>0.2890678950734066</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2384066840225015</v>
+        <v>0.2403066840225014</v>
       </c>
       <c r="C98">
-        <v>-2886.636040482709</v>
+        <v>-2938.314892930799</v>
       </c>
       <c r="D98">
-        <v>1124.08795951729</v>
+        <v>1114.328107069201</v>
       </c>
       <c r="E98">
-        <v>2951.424</v>
+        <v>2993.343</v>
       </c>
       <c r="F98">
-        <v>4024.224</v>
+        <v>4066.143</v>
       </c>
       <c r="G98">
         <v>13.5</v>
@@ -9323,37 +9323,37 @@
         <v>274.3</v>
       </c>
       <c r="M98">
-        <v>948.9120191999999</v>
+        <v>958.7965194</v>
       </c>
       <c r="N98">
-        <v>-674.6120191999998</v>
+        <v>-684.4965193999999</v>
       </c>
       <c r="O98">
-        <v>-215.875846144</v>
+        <v>-219.038886208</v>
       </c>
       <c r="P98">
-        <v>-458.7361730559999</v>
+        <v>-465.4576331919999</v>
       </c>
       <c r="Q98">
-        <v>-372.4361730559999</v>
+        <v>-379.1576331919999</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.8244528707383509</v>
+        <v>1.084003827651135</v>
       </c>
       <c r="T98">
-        <v>10.14845718487767</v>
+        <v>13.53127624650356</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.09250172642349012</v>
+        <v>0.09154810037788715</v>
       </c>
       <c r="W98">
-        <v>0.213988092909341</v>
+        <v>0.2142129579308942</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.2890678950734067</v>
+        <v>0.2860878136808973</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2403066840225014</v>
+        <v>0.2422066840225015</v>
       </c>
       <c r="C99">
-        <v>-2938.314892930799</v>
+        <v>-2989.825725087623</v>
       </c>
       <c r="D99">
-        <v>1114.328107069201</v>
+        <v>1104.736274912377</v>
       </c>
       <c r="E99">
-        <v>2993.343</v>
+        <v>3035.262</v>
       </c>
       <c r="F99">
-        <v>4066.143</v>
+        <v>4108.062</v>
       </c>
       <c r="G99">
         <v>13.5</v>
@@ -9405,37 +9405,37 @@
         <v>274.3</v>
       </c>
       <c r="M99">
-        <v>958.7965194</v>
+        <v>968.6810196</v>
       </c>
       <c r="N99">
-        <v>-684.4965193999999</v>
+        <v>-694.3810195999999</v>
       </c>
       <c r="O99">
-        <v>-219.038886208</v>
+        <v>-222.201926272</v>
       </c>
       <c r="P99">
-        <v>-465.4576331919999</v>
+        <v>-472.179093328</v>
       </c>
       <c r="Q99">
-        <v>-379.1576331919999</v>
+        <v>-385.879093328</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.084003827651135</v>
+        <v>1.603105741476702</v>
       </c>
       <c r="T99">
-        <v>13.53127624650356</v>
+        <v>20.29691436975534</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.09154810037788715</v>
+        <v>0.09061393608831685</v>
       </c>
       <c r="W99">
-        <v>0.2142129579308942</v>
+        <v>0.2144332338703749</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.2860878136808973</v>
+        <v>0.2831685502759902</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2422066840225015</v>
+        <v>0.2441066840225015</v>
       </c>
       <c r="C100">
-        <v>-2989.825725087623</v>
+        <v>-3041.172838742954</v>
       </c>
       <c r="D100">
-        <v>1104.736274912377</v>
+        <v>1095.308161257046</v>
       </c>
       <c r="E100">
-        <v>3035.262</v>
+        <v>3077.181</v>
       </c>
       <c r="F100">
-        <v>4108.062</v>
+        <v>4149.981</v>
       </c>
       <c r="G100">
         <v>13.5</v>
@@ -9487,37 +9487,37 @@
         <v>274.3</v>
       </c>
       <c r="M100">
-        <v>968.6810196</v>
+        <v>978.5655197999999</v>
       </c>
       <c r="N100">
-        <v>-694.3810195999999</v>
+        <v>-704.2655198</v>
       </c>
       <c r="O100">
-        <v>-222.201926272</v>
+        <v>-225.364966336</v>
       </c>
       <c r="P100">
-        <v>-472.179093328</v>
+        <v>-478.900553464</v>
       </c>
       <c r="Q100">
-        <v>-385.879093328</v>
+        <v>-392.600553464</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.603105741476702</v>
+        <v>3.160411482953404</v>
       </c>
       <c r="T100">
-        <v>20.29691436975534</v>
+        <v>40.59382873951068</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.09061393608831685</v>
+        <v>0.0896986438045965</v>
       </c>
       <c r="W100">
-        <v>0.2144332338703749</v>
+        <v>0.2146490597908762</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.2831685502759902</v>
+        <v>0.280308261889364</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2441066840225015</v>
-      </c>
-      <c r="C101">
-        <v>-3041.172838742954</v>
-      </c>
-      <c r="D101">
-        <v>1095.308161257046</v>
-      </c>
-      <c r="E101">
-        <v>3077.181</v>
-      </c>
-      <c r="F101">
-        <v>4149.981</v>
-      </c>
-      <c r="G101">
-        <v>13.5</v>
-      </c>
-      <c r="H101">
-        <v>3119.1</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>360.6</v>
-      </c>
-      <c r="K101">
-        <v>86.3</v>
-      </c>
-      <c r="L101">
-        <v>274.3</v>
-      </c>
-      <c r="M101">
-        <v>978.5655197999999</v>
-      </c>
-      <c r="N101">
-        <v>-704.2655198</v>
-      </c>
-      <c r="O101">
-        <v>-225.364966336</v>
-      </c>
-      <c r="P101">
-        <v>-478.900553464</v>
-      </c>
-      <c r="Q101">
-        <v>-392.600553464</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>3.160411482953404</v>
-      </c>
-      <c r="T101">
-        <v>40.59382873951068</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.0896986438045965</v>
-      </c>
-      <c r="W101">
-        <v>0.2146490597908762</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.280308261889364</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
